--- a/ig/DM-JUIN-2026/CodeSystem-terminologie-nabm.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-terminologie-nabm.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3268" uniqueCount="2192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="2199">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>V104</t>
+    <t>V105</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T00:00:00+00:00</t>
+    <t>2026-06-04T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1046</t>
+    <t>1050</t>
   </si>
   <si>
     <t>Code</t>
@@ -2690,6 +2690,12 @@
     <t>EXAMEN ANATOMOPATHOLOGIQUE PAR HYBRIDATION IN SITU</t>
   </si>
   <si>
+    <t>4515</t>
+  </si>
+  <si>
+    <t>SHD DANS LE DIAGNOSTIC DES FORMES DIVERSES DE CARDIOMYOPATHIES</t>
+  </si>
+  <si>
     <t>0024</t>
   </si>
   <si>
@@ -3276,6 +3282,12 @@
   </si>
   <si>
     <t>UR. : CUIVRE</t>
+  </si>
+  <si>
+    <t>4514</t>
+  </si>
+  <si>
+    <t>SHD DANS LE DIAGNOSTIC DES CARDIOMYOPATHIES HYPERTROPHIQUES</t>
   </si>
   <si>
     <t>0463</t>
@@ -4330,9 +4342,6 @@
     <t>HEPATITE C (VHC) : DETECTION QUANTITATIVE GENOME (ARN):</t>
   </si>
   <si>
-    <t>1050</t>
-  </si>
-  <si>
     <t>MESURE DE L'ACTIVITE D'ADAMTS 13</t>
   </si>
   <si>
@@ -6308,6 +6317,12 @@
     <t>PROTOPORPHYRINES ZINC (PPZ)</t>
   </si>
   <si>
+    <t>1692</t>
+  </si>
+  <si>
+    <t>DOSAGE URINAIRE DU CADMIUM (CADMIURIE)</t>
+  </si>
+  <si>
     <t>1014</t>
   </si>
   <si>
@@ -6396,6 +6411,12 @@
   </si>
   <si>
     <t>PARAINFLUENZA (PARAMYXOVIRUS) : SD PAR RFC + ITERATIF</t>
+  </si>
+  <si>
+    <t>1693</t>
+  </si>
+  <si>
+    <t>DOSAGE DANS LE SANG TOTAL DU CADMIUM (CADMIEMIE)</t>
   </si>
   <si>
     <t>8000</t>
@@ -7231,7 +7252,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1047"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -15303,10 +15324,10 @@
         <v>96</v>
       </c>
       <c r="B672" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="C672" t="s" s="2">
         <v>1441</v>
-      </c>
-      <c r="C672" t="s" s="2">
-        <v>1442</v>
       </c>
       <c r="D672" s="2"/>
     </row>
@@ -15315,10 +15336,10 @@
         <v>96</v>
       </c>
       <c r="B673" t="s" s="2">
+        <v>1442</v>
+      </c>
+      <c r="C673" t="s" s="2">
         <v>1443</v>
-      </c>
-      <c r="C673" t="s" s="2">
-        <v>1444</v>
       </c>
       <c r="D673" s="2"/>
     </row>
@@ -15327,10 +15348,10 @@
         <v>96</v>
       </c>
       <c r="B674" t="s" s="2">
+        <v>1444</v>
+      </c>
+      <c r="C674" t="s" s="2">
         <v>1445</v>
-      </c>
-      <c r="C674" t="s" s="2">
-        <v>1446</v>
       </c>
       <c r="D674" s="2"/>
     </row>
@@ -15339,10 +15360,10 @@
         <v>96</v>
       </c>
       <c r="B675" t="s" s="2">
+        <v>1446</v>
+      </c>
+      <c r="C675" t="s" s="2">
         <v>1447</v>
-      </c>
-      <c r="C675" t="s" s="2">
-        <v>1448</v>
       </c>
       <c r="D675" s="2"/>
     </row>
@@ -15351,10 +15372,10 @@
         <v>96</v>
       </c>
       <c r="B676" t="s" s="2">
+        <v>1448</v>
+      </c>
+      <c r="C676" t="s" s="2">
         <v>1449</v>
-      </c>
-      <c r="C676" t="s" s="2">
-        <v>1450</v>
       </c>
       <c r="D676" s="2"/>
     </row>
@@ -15363,10 +15384,10 @@
         <v>96</v>
       </c>
       <c r="B677" t="s" s="2">
+        <v>1450</v>
+      </c>
+      <c r="C677" t="s" s="2">
         <v>1451</v>
-      </c>
-      <c r="C677" t="s" s="2">
-        <v>1452</v>
       </c>
       <c r="D677" s="2"/>
     </row>
@@ -15375,10 +15396,10 @@
         <v>96</v>
       </c>
       <c r="B678" t="s" s="2">
+        <v>1452</v>
+      </c>
+      <c r="C678" t="s" s="2">
         <v>1453</v>
-      </c>
-      <c r="C678" t="s" s="2">
-        <v>1454</v>
       </c>
       <c r="D678" s="2"/>
     </row>
@@ -15387,10 +15408,10 @@
         <v>96</v>
       </c>
       <c r="B679" t="s" s="2">
+        <v>1454</v>
+      </c>
+      <c r="C679" t="s" s="2">
         <v>1455</v>
-      </c>
-      <c r="C679" t="s" s="2">
-        <v>1456</v>
       </c>
       <c r="D679" s="2"/>
     </row>
@@ -15399,10 +15420,10 @@
         <v>96</v>
       </c>
       <c r="B680" t="s" s="2">
+        <v>1456</v>
+      </c>
+      <c r="C680" t="s" s="2">
         <v>1457</v>
-      </c>
-      <c r="C680" t="s" s="2">
-        <v>1458</v>
       </c>
       <c r="D680" s="2"/>
     </row>
@@ -15411,10 +15432,10 @@
         <v>96</v>
       </c>
       <c r="B681" t="s" s="2">
+        <v>1458</v>
+      </c>
+      <c r="C681" t="s" s="2">
         <v>1459</v>
-      </c>
-      <c r="C681" t="s" s="2">
-        <v>1460</v>
       </c>
       <c r="D681" s="2"/>
     </row>
@@ -15423,10 +15444,10 @@
         <v>96</v>
       </c>
       <c r="B682" t="s" s="2">
+        <v>1460</v>
+      </c>
+      <c r="C682" t="s" s="2">
         <v>1461</v>
-      </c>
-      <c r="C682" t="s" s="2">
-        <v>1462</v>
       </c>
       <c r="D682" s="2"/>
     </row>
@@ -15435,10 +15456,10 @@
         <v>96</v>
       </c>
       <c r="B683" t="s" s="2">
+        <v>1462</v>
+      </c>
+      <c r="C683" t="s" s="2">
         <v>1463</v>
-      </c>
-      <c r="C683" t="s" s="2">
-        <v>1464</v>
       </c>
       <c r="D683" s="2"/>
     </row>
@@ -15447,10 +15468,10 @@
         <v>96</v>
       </c>
       <c r="B684" t="s" s="2">
+        <v>1464</v>
+      </c>
+      <c r="C684" t="s" s="2">
         <v>1465</v>
-      </c>
-      <c r="C684" t="s" s="2">
-        <v>1466</v>
       </c>
       <c r="D684" s="2"/>
     </row>
@@ -15459,10 +15480,10 @@
         <v>96</v>
       </c>
       <c r="B685" t="s" s="2">
+        <v>1466</v>
+      </c>
+      <c r="C685" t="s" s="2">
         <v>1467</v>
-      </c>
-      <c r="C685" t="s" s="2">
-        <v>1468</v>
       </c>
       <c r="D685" s="2"/>
     </row>
@@ -15471,10 +15492,10 @@
         <v>96</v>
       </c>
       <c r="B686" t="s" s="2">
+        <v>1468</v>
+      </c>
+      <c r="C686" t="s" s="2">
         <v>1469</v>
-      </c>
-      <c r="C686" t="s" s="2">
-        <v>1470</v>
       </c>
       <c r="D686" s="2"/>
     </row>
@@ -15483,10 +15504,10 @@
         <v>96</v>
       </c>
       <c r="B687" t="s" s="2">
+        <v>1470</v>
+      </c>
+      <c r="C687" t="s" s="2">
         <v>1471</v>
-      </c>
-      <c r="C687" t="s" s="2">
-        <v>1472</v>
       </c>
       <c r="D687" s="2"/>
     </row>
@@ -15495,10 +15516,10 @@
         <v>96</v>
       </c>
       <c r="B688" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="C688" t="s" s="2">
         <v>1473</v>
-      </c>
-      <c r="C688" t="s" s="2">
-        <v>1474</v>
       </c>
       <c r="D688" s="2"/>
     </row>
@@ -15507,10 +15528,10 @@
         <v>96</v>
       </c>
       <c r="B689" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="C689" t="s" s="2">
         <v>1475</v>
-      </c>
-      <c r="C689" t="s" s="2">
-        <v>1476</v>
       </c>
       <c r="D689" s="2"/>
     </row>
@@ -15519,10 +15540,10 @@
         <v>96</v>
       </c>
       <c r="B690" t="s" s="2">
+        <v>1476</v>
+      </c>
+      <c r="C690" t="s" s="2">
         <v>1477</v>
-      </c>
-      <c r="C690" t="s" s="2">
-        <v>1478</v>
       </c>
       <c r="D690" s="2"/>
     </row>
@@ -15531,10 +15552,10 @@
         <v>96</v>
       </c>
       <c r="B691" t="s" s="2">
+        <v>1478</v>
+      </c>
+      <c r="C691" t="s" s="2">
         <v>1479</v>
-      </c>
-      <c r="C691" t="s" s="2">
-        <v>1480</v>
       </c>
       <c r="D691" s="2"/>
     </row>
@@ -15543,10 +15564,10 @@
         <v>96</v>
       </c>
       <c r="B692" t="s" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C692" t="s" s="2">
         <v>1481</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>1482</v>
       </c>
       <c r="D692" s="2"/>
     </row>
@@ -15555,10 +15576,10 @@
         <v>96</v>
       </c>
       <c r="B693" t="s" s="2">
+        <v>1482</v>
+      </c>
+      <c r="C693" t="s" s="2">
         <v>1483</v>
-      </c>
-      <c r="C693" t="s" s="2">
-        <v>1484</v>
       </c>
       <c r="D693" s="2"/>
     </row>
@@ -15567,10 +15588,10 @@
         <v>96</v>
       </c>
       <c r="B694" t="s" s="2">
+        <v>1484</v>
+      </c>
+      <c r="C694" t="s" s="2">
         <v>1485</v>
-      </c>
-      <c r="C694" t="s" s="2">
-        <v>1486</v>
       </c>
       <c r="D694" s="2"/>
     </row>
@@ -15579,10 +15600,10 @@
         <v>96</v>
       </c>
       <c r="B695" t="s" s="2">
+        <v>1486</v>
+      </c>
+      <c r="C695" t="s" s="2">
         <v>1487</v>
-      </c>
-      <c r="C695" t="s" s="2">
-        <v>1488</v>
       </c>
       <c r="D695" s="2"/>
     </row>
@@ -15591,10 +15612,10 @@
         <v>96</v>
       </c>
       <c r="B696" t="s" s="2">
+        <v>1488</v>
+      </c>
+      <c r="C696" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="C696" t="s" s="2">
-        <v>1490</v>
       </c>
       <c r="D696" s="2"/>
     </row>
@@ -15603,10 +15624,10 @@
         <v>96</v>
       </c>
       <c r="B697" t="s" s="2">
+        <v>1490</v>
+      </c>
+      <c r="C697" t="s" s="2">
         <v>1491</v>
-      </c>
-      <c r="C697" t="s" s="2">
-        <v>1492</v>
       </c>
       <c r="D697" s="2"/>
     </row>
@@ -15615,10 +15636,10 @@
         <v>96</v>
       </c>
       <c r="B698" t="s" s="2">
+        <v>1492</v>
+      </c>
+      <c r="C698" t="s" s="2">
         <v>1493</v>
-      </c>
-      <c r="C698" t="s" s="2">
-        <v>1494</v>
       </c>
       <c r="D698" s="2"/>
     </row>
@@ -15627,10 +15648,10 @@
         <v>96</v>
       </c>
       <c r="B699" t="s" s="2">
+        <v>1494</v>
+      </c>
+      <c r="C699" t="s" s="2">
         <v>1495</v>
-      </c>
-      <c r="C699" t="s" s="2">
-        <v>1496</v>
       </c>
       <c r="D699" s="2"/>
     </row>
@@ -15639,10 +15660,10 @@
         <v>96</v>
       </c>
       <c r="B700" t="s" s="2">
+        <v>1496</v>
+      </c>
+      <c r="C700" t="s" s="2">
         <v>1497</v>
-      </c>
-      <c r="C700" t="s" s="2">
-        <v>1498</v>
       </c>
       <c r="D700" s="2"/>
     </row>
@@ -15651,10 +15672,10 @@
         <v>96</v>
       </c>
       <c r="B701" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="C701" t="s" s="2">
         <v>1499</v>
-      </c>
-      <c r="C701" t="s" s="2">
-        <v>1500</v>
       </c>
       <c r="D701" s="2"/>
     </row>
@@ -15663,10 +15684,10 @@
         <v>96</v>
       </c>
       <c r="B702" t="s" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C702" t="s" s="2">
         <v>1501</v>
-      </c>
-      <c r="C702" t="s" s="2">
-        <v>1502</v>
       </c>
       <c r="D702" s="2"/>
     </row>
@@ -15675,10 +15696,10 @@
         <v>96</v>
       </c>
       <c r="B703" t="s" s="2">
+        <v>1502</v>
+      </c>
+      <c r="C703" t="s" s="2">
         <v>1503</v>
-      </c>
-      <c r="C703" t="s" s="2">
-        <v>1504</v>
       </c>
       <c r="D703" s="2"/>
     </row>
@@ -15687,10 +15708,10 @@
         <v>96</v>
       </c>
       <c r="B704" t="s" s="2">
+        <v>1504</v>
+      </c>
+      <c r="C704" t="s" s="2">
         <v>1505</v>
-      </c>
-      <c r="C704" t="s" s="2">
-        <v>1506</v>
       </c>
       <c r="D704" s="2"/>
     </row>
@@ -15699,10 +15720,10 @@
         <v>96</v>
       </c>
       <c r="B705" t="s" s="2">
+        <v>1506</v>
+      </c>
+      <c r="C705" t="s" s="2">
         <v>1507</v>
-      </c>
-      <c r="C705" t="s" s="2">
-        <v>1508</v>
       </c>
       <c r="D705" s="2"/>
     </row>
@@ -15711,10 +15732,10 @@
         <v>96</v>
       </c>
       <c r="B706" t="s" s="2">
+        <v>1508</v>
+      </c>
+      <c r="C706" t="s" s="2">
         <v>1509</v>
-      </c>
-      <c r="C706" t="s" s="2">
-        <v>1510</v>
       </c>
       <c r="D706" s="2"/>
     </row>
@@ -15723,10 +15744,10 @@
         <v>96</v>
       </c>
       <c r="B707" t="s" s="2">
+        <v>1510</v>
+      </c>
+      <c r="C707" t="s" s="2">
         <v>1511</v>
-      </c>
-      <c r="C707" t="s" s="2">
-        <v>1512</v>
       </c>
       <c r="D707" s="2"/>
     </row>
@@ -15735,10 +15756,10 @@
         <v>96</v>
       </c>
       <c r="B708" t="s" s="2">
+        <v>1512</v>
+      </c>
+      <c r="C708" t="s" s="2">
         <v>1513</v>
-      </c>
-      <c r="C708" t="s" s="2">
-        <v>1514</v>
       </c>
       <c r="D708" s="2"/>
     </row>
@@ -15747,10 +15768,10 @@
         <v>96</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1514</v>
+      </c>
+      <c r="C709" t="s" s="2">
         <v>1515</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1516</v>
       </c>
       <c r="D709" s="2"/>
     </row>
@@ -15759,10 +15780,10 @@
         <v>96</v>
       </c>
       <c r="B710" t="s" s="2">
+        <v>1516</v>
+      </c>
+      <c r="C710" t="s" s="2">
         <v>1517</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1518</v>
       </c>
       <c r="D710" s="2"/>
     </row>
@@ -15771,10 +15792,10 @@
         <v>96</v>
       </c>
       <c r="B711" t="s" s="2">
+        <v>1518</v>
+      </c>
+      <c r="C711" t="s" s="2">
         <v>1519</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1520</v>
       </c>
       <c r="D711" s="2"/>
     </row>
@@ -15783,10 +15804,10 @@
         <v>96</v>
       </c>
       <c r="B712" t="s" s="2">
+        <v>1520</v>
+      </c>
+      <c r="C712" t="s" s="2">
         <v>1521</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1522</v>
       </c>
       <c r="D712" s="2"/>
     </row>
@@ -15795,10 +15816,10 @@
         <v>96</v>
       </c>
       <c r="B713" t="s" s="2">
+        <v>1522</v>
+      </c>
+      <c r="C713" t="s" s="2">
         <v>1523</v>
-      </c>
-      <c r="C713" t="s" s="2">
-        <v>1524</v>
       </c>
       <c r="D713" s="2"/>
     </row>
@@ -15807,10 +15828,10 @@
         <v>96</v>
       </c>
       <c r="B714" t="s" s="2">
+        <v>1524</v>
+      </c>
+      <c r="C714" t="s" s="2">
         <v>1525</v>
-      </c>
-      <c r="C714" t="s" s="2">
-        <v>1526</v>
       </c>
       <c r="D714" s="2"/>
     </row>
@@ -15819,10 +15840,10 @@
         <v>96</v>
       </c>
       <c r="B715" t="s" s="2">
+        <v>1526</v>
+      </c>
+      <c r="C715" t="s" s="2">
         <v>1527</v>
-      </c>
-      <c r="C715" t="s" s="2">
-        <v>1528</v>
       </c>
       <c r="D715" s="2"/>
     </row>
@@ -15831,10 +15852,10 @@
         <v>96</v>
       </c>
       <c r="B716" t="s" s="2">
+        <v>1528</v>
+      </c>
+      <c r="C716" t="s" s="2">
         <v>1529</v>
-      </c>
-      <c r="C716" t="s" s="2">
-        <v>1530</v>
       </c>
       <c r="D716" s="2"/>
     </row>
@@ -15843,10 +15864,10 @@
         <v>96</v>
       </c>
       <c r="B717" t="s" s="2">
+        <v>1530</v>
+      </c>
+      <c r="C717" t="s" s="2">
         <v>1531</v>
-      </c>
-      <c r="C717" t="s" s="2">
-        <v>1532</v>
       </c>
       <c r="D717" s="2"/>
     </row>
@@ -15855,10 +15876,10 @@
         <v>96</v>
       </c>
       <c r="B718" t="s" s="2">
+        <v>1532</v>
+      </c>
+      <c r="C718" t="s" s="2">
         <v>1533</v>
-      </c>
-      <c r="C718" t="s" s="2">
-        <v>1534</v>
       </c>
       <c r="D718" s="2"/>
     </row>
@@ -15867,10 +15888,10 @@
         <v>96</v>
       </c>
       <c r="B719" t="s" s="2">
+        <v>1534</v>
+      </c>
+      <c r="C719" t="s" s="2">
         <v>1535</v>
-      </c>
-      <c r="C719" t="s" s="2">
-        <v>1536</v>
       </c>
       <c r="D719" s="2"/>
     </row>
@@ -15879,10 +15900,10 @@
         <v>96</v>
       </c>
       <c r="B720" t="s" s="2">
+        <v>1536</v>
+      </c>
+      <c r="C720" t="s" s="2">
         <v>1537</v>
-      </c>
-      <c r="C720" t="s" s="2">
-        <v>1538</v>
       </c>
       <c r="D720" s="2"/>
     </row>
@@ -15891,10 +15912,10 @@
         <v>96</v>
       </c>
       <c r="B721" t="s" s="2">
+        <v>1538</v>
+      </c>
+      <c r="C721" t="s" s="2">
         <v>1539</v>
-      </c>
-      <c r="C721" t="s" s="2">
-        <v>1540</v>
       </c>
       <c r="D721" s="2"/>
     </row>
@@ -15903,10 +15924,10 @@
         <v>96</v>
       </c>
       <c r="B722" t="s" s="2">
+        <v>1540</v>
+      </c>
+      <c r="C722" t="s" s="2">
         <v>1541</v>
-      </c>
-      <c r="C722" t="s" s="2">
-        <v>1542</v>
       </c>
       <c r="D722" s="2"/>
     </row>
@@ -15915,10 +15936,10 @@
         <v>96</v>
       </c>
       <c r="B723" t="s" s="2">
+        <v>1542</v>
+      </c>
+      <c r="C723" t="s" s="2">
         <v>1543</v>
-      </c>
-      <c r="C723" t="s" s="2">
-        <v>1544</v>
       </c>
       <c r="D723" s="2"/>
     </row>
@@ -15927,10 +15948,10 @@
         <v>96</v>
       </c>
       <c r="B724" t="s" s="2">
+        <v>1544</v>
+      </c>
+      <c r="C724" t="s" s="2">
         <v>1545</v>
-      </c>
-      <c r="C724" t="s" s="2">
-        <v>1546</v>
       </c>
       <c r="D724" s="2"/>
     </row>
@@ -15939,10 +15960,10 @@
         <v>96</v>
       </c>
       <c r="B725" t="s" s="2">
+        <v>1546</v>
+      </c>
+      <c r="C725" t="s" s="2">
         <v>1547</v>
-      </c>
-      <c r="C725" t="s" s="2">
-        <v>1548</v>
       </c>
       <c r="D725" s="2"/>
     </row>
@@ -15951,10 +15972,10 @@
         <v>96</v>
       </c>
       <c r="B726" t="s" s="2">
+        <v>1548</v>
+      </c>
+      <c r="C726" t="s" s="2">
         <v>1549</v>
-      </c>
-      <c r="C726" t="s" s="2">
-        <v>1550</v>
       </c>
       <c r="D726" s="2"/>
     </row>
@@ -15963,10 +15984,10 @@
         <v>96</v>
       </c>
       <c r="B727" t="s" s="2">
+        <v>1550</v>
+      </c>
+      <c r="C727" t="s" s="2">
         <v>1551</v>
-      </c>
-      <c r="C727" t="s" s="2">
-        <v>1552</v>
       </c>
       <c r="D727" s="2"/>
     </row>
@@ -15975,10 +15996,10 @@
         <v>96</v>
       </c>
       <c r="B728" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="C728" t="s" s="2">
         <v>1553</v>
-      </c>
-      <c r="C728" t="s" s="2">
-        <v>1554</v>
       </c>
       <c r="D728" s="2"/>
     </row>
@@ -15987,10 +16008,10 @@
         <v>96</v>
       </c>
       <c r="B729" t="s" s="2">
+        <v>1554</v>
+      </c>
+      <c r="C729" t="s" s="2">
         <v>1555</v>
-      </c>
-      <c r="C729" t="s" s="2">
-        <v>1556</v>
       </c>
       <c r="D729" s="2"/>
     </row>
@@ -15999,10 +16020,10 @@
         <v>96</v>
       </c>
       <c r="B730" t="s" s="2">
+        <v>1556</v>
+      </c>
+      <c r="C730" t="s" s="2">
         <v>1557</v>
-      </c>
-      <c r="C730" t="s" s="2">
-        <v>1558</v>
       </c>
       <c r="D730" s="2"/>
     </row>
@@ -16011,10 +16032,10 @@
         <v>96</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1558</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1559</v>
-      </c>
-      <c r="C731" t="s" s="2">
-        <v>1560</v>
       </c>
       <c r="D731" s="2"/>
     </row>
@@ -16023,10 +16044,10 @@
         <v>96</v>
       </c>
       <c r="B732" t="s" s="2">
+        <v>1560</v>
+      </c>
+      <c r="C732" t="s" s="2">
         <v>1561</v>
-      </c>
-      <c r="C732" t="s" s="2">
-        <v>1562</v>
       </c>
       <c r="D732" s="2"/>
     </row>
@@ -16035,10 +16056,10 @@
         <v>96</v>
       </c>
       <c r="B733" t="s" s="2">
+        <v>1562</v>
+      </c>
+      <c r="C733" t="s" s="2">
         <v>1563</v>
-      </c>
-      <c r="C733" t="s" s="2">
-        <v>1564</v>
       </c>
       <c r="D733" s="2"/>
     </row>
@@ -16047,10 +16068,10 @@
         <v>96</v>
       </c>
       <c r="B734" t="s" s="2">
+        <v>1564</v>
+      </c>
+      <c r="C734" t="s" s="2">
         <v>1565</v>
-      </c>
-      <c r="C734" t="s" s="2">
-        <v>1566</v>
       </c>
       <c r="D734" s="2"/>
     </row>
@@ -16059,10 +16080,10 @@
         <v>96</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1566</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1567</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1568</v>
       </c>
       <c r="D735" s="2"/>
     </row>
@@ -16071,10 +16092,10 @@
         <v>96</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1568</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1569</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1570</v>
       </c>
       <c r="D736" s="2"/>
     </row>
@@ -16083,10 +16104,10 @@
         <v>96</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1570</v>
+      </c>
+      <c r="C737" t="s" s="2">
         <v>1571</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1572</v>
       </c>
       <c r="D737" s="2"/>
     </row>
@@ -16095,10 +16116,10 @@
         <v>96</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1572</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1573</v>
-      </c>
-      <c r="C738" t="s" s="2">
-        <v>1574</v>
       </c>
       <c r="D738" s="2"/>
     </row>
@@ -16107,10 +16128,10 @@
         <v>96</v>
       </c>
       <c r="B739" t="s" s="2">
+        <v>1574</v>
+      </c>
+      <c r="C739" t="s" s="2">
         <v>1575</v>
-      </c>
-      <c r="C739" t="s" s="2">
-        <v>1576</v>
       </c>
       <c r="D739" s="2"/>
     </row>
@@ -16119,10 +16140,10 @@
         <v>96</v>
       </c>
       <c r="B740" t="s" s="2">
+        <v>1576</v>
+      </c>
+      <c r="C740" t="s" s="2">
         <v>1577</v>
-      </c>
-      <c r="C740" t="s" s="2">
-        <v>1578</v>
       </c>
       <c r="D740" s="2"/>
     </row>
@@ -16131,10 +16152,10 @@
         <v>96</v>
       </c>
       <c r="B741" t="s" s="2">
+        <v>1578</v>
+      </c>
+      <c r="C741" t="s" s="2">
         <v>1579</v>
-      </c>
-      <c r="C741" t="s" s="2">
-        <v>1580</v>
       </c>
       <c r="D741" s="2"/>
     </row>
@@ -16143,10 +16164,10 @@
         <v>96</v>
       </c>
       <c r="B742" t="s" s="2">
+        <v>1580</v>
+      </c>
+      <c r="C742" t="s" s="2">
         <v>1581</v>
-      </c>
-      <c r="C742" t="s" s="2">
-        <v>1582</v>
       </c>
       <c r="D742" s="2"/>
     </row>
@@ -16155,10 +16176,10 @@
         <v>96</v>
       </c>
       <c r="B743" t="s" s="2">
+        <v>1582</v>
+      </c>
+      <c r="C743" t="s" s="2">
         <v>1583</v>
-      </c>
-      <c r="C743" t="s" s="2">
-        <v>1584</v>
       </c>
       <c r="D743" s="2"/>
     </row>
@@ -16167,10 +16188,10 @@
         <v>96</v>
       </c>
       <c r="B744" t="s" s="2">
+        <v>1584</v>
+      </c>
+      <c r="C744" t="s" s="2">
         <v>1585</v>
-      </c>
-      <c r="C744" t="s" s="2">
-        <v>1586</v>
       </c>
       <c r="D744" s="2"/>
     </row>
@@ -16179,10 +16200,10 @@
         <v>96</v>
       </c>
       <c r="B745" t="s" s="2">
+        <v>1586</v>
+      </c>
+      <c r="C745" t="s" s="2">
         <v>1587</v>
-      </c>
-      <c r="C745" t="s" s="2">
-        <v>1588</v>
       </c>
       <c r="D745" s="2"/>
     </row>
@@ -16191,10 +16212,10 @@
         <v>96</v>
       </c>
       <c r="B746" t="s" s="2">
+        <v>1588</v>
+      </c>
+      <c r="C746" t="s" s="2">
         <v>1589</v>
-      </c>
-      <c r="C746" t="s" s="2">
-        <v>1590</v>
       </c>
       <c r="D746" s="2"/>
     </row>
@@ -16203,10 +16224,10 @@
         <v>96</v>
       </c>
       <c r="B747" t="s" s="2">
+        <v>1590</v>
+      </c>
+      <c r="C747" t="s" s="2">
         <v>1591</v>
-      </c>
-      <c r="C747" t="s" s="2">
-        <v>1592</v>
       </c>
       <c r="D747" s="2"/>
     </row>
@@ -16215,10 +16236,10 @@
         <v>96</v>
       </c>
       <c r="B748" t="s" s="2">
+        <v>1592</v>
+      </c>
+      <c r="C748" t="s" s="2">
         <v>1593</v>
-      </c>
-      <c r="C748" t="s" s="2">
-        <v>1594</v>
       </c>
       <c r="D748" s="2"/>
     </row>
@@ -16227,10 +16248,10 @@
         <v>96</v>
       </c>
       <c r="B749" t="s" s="2">
+        <v>1594</v>
+      </c>
+      <c r="C749" t="s" s="2">
         <v>1595</v>
-      </c>
-      <c r="C749" t="s" s="2">
-        <v>1596</v>
       </c>
       <c r="D749" s="2"/>
     </row>
@@ -16239,10 +16260,10 @@
         <v>96</v>
       </c>
       <c r="B750" t="s" s="2">
+        <v>1596</v>
+      </c>
+      <c r="C750" t="s" s="2">
         <v>1597</v>
-      </c>
-      <c r="C750" t="s" s="2">
-        <v>1598</v>
       </c>
       <c r="D750" s="2"/>
     </row>
@@ -16251,10 +16272,10 @@
         <v>96</v>
       </c>
       <c r="B751" t="s" s="2">
+        <v>1598</v>
+      </c>
+      <c r="C751" t="s" s="2">
         <v>1599</v>
-      </c>
-      <c r="C751" t="s" s="2">
-        <v>1600</v>
       </c>
       <c r="D751" s="2"/>
     </row>
@@ -16263,10 +16284,10 @@
         <v>96</v>
       </c>
       <c r="B752" t="s" s="2">
+        <v>1600</v>
+      </c>
+      <c r="C752" t="s" s="2">
         <v>1601</v>
-      </c>
-      <c r="C752" t="s" s="2">
-        <v>1602</v>
       </c>
       <c r="D752" s="2"/>
     </row>
@@ -16275,10 +16296,10 @@
         <v>96</v>
       </c>
       <c r="B753" t="s" s="2">
+        <v>1602</v>
+      </c>
+      <c r="C753" t="s" s="2">
         <v>1603</v>
-      </c>
-      <c r="C753" t="s" s="2">
-        <v>1604</v>
       </c>
       <c r="D753" s="2"/>
     </row>
@@ -16287,10 +16308,10 @@
         <v>96</v>
       </c>
       <c r="B754" t="s" s="2">
+        <v>1604</v>
+      </c>
+      <c r="C754" t="s" s="2">
         <v>1605</v>
-      </c>
-      <c r="C754" t="s" s="2">
-        <v>1606</v>
       </c>
       <c r="D754" s="2"/>
     </row>
@@ -16299,10 +16320,10 @@
         <v>96</v>
       </c>
       <c r="B755" t="s" s="2">
+        <v>1606</v>
+      </c>
+      <c r="C755" t="s" s="2">
         <v>1607</v>
-      </c>
-      <c r="C755" t="s" s="2">
-        <v>1608</v>
       </c>
       <c r="D755" s="2"/>
     </row>
@@ -16311,10 +16332,10 @@
         <v>96</v>
       </c>
       <c r="B756" t="s" s="2">
+        <v>1608</v>
+      </c>
+      <c r="C756" t="s" s="2">
         <v>1609</v>
-      </c>
-      <c r="C756" t="s" s="2">
-        <v>1610</v>
       </c>
       <c r="D756" s="2"/>
     </row>
@@ -16323,10 +16344,10 @@
         <v>96</v>
       </c>
       <c r="B757" t="s" s="2">
+        <v>1610</v>
+      </c>
+      <c r="C757" t="s" s="2">
         <v>1611</v>
-      </c>
-      <c r="C757" t="s" s="2">
-        <v>1612</v>
       </c>
       <c r="D757" s="2"/>
     </row>
@@ -16335,10 +16356,10 @@
         <v>96</v>
       </c>
       <c r="B758" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="C758" t="s" s="2">
         <v>1613</v>
-      </c>
-      <c r="C758" t="s" s="2">
-        <v>1614</v>
       </c>
       <c r="D758" s="2"/>
     </row>
@@ -16347,10 +16368,10 @@
         <v>96</v>
       </c>
       <c r="B759" t="s" s="2">
+        <v>1614</v>
+      </c>
+      <c r="C759" t="s" s="2">
         <v>1615</v>
-      </c>
-      <c r="C759" t="s" s="2">
-        <v>1616</v>
       </c>
       <c r="D759" s="2"/>
     </row>
@@ -16359,10 +16380,10 @@
         <v>96</v>
       </c>
       <c r="B760" t="s" s="2">
+        <v>1616</v>
+      </c>
+      <c r="C760" t="s" s="2">
         <v>1617</v>
-      </c>
-      <c r="C760" t="s" s="2">
-        <v>1618</v>
       </c>
       <c r="D760" s="2"/>
     </row>
@@ -16371,10 +16392,10 @@
         <v>96</v>
       </c>
       <c r="B761" t="s" s="2">
+        <v>1618</v>
+      </c>
+      <c r="C761" t="s" s="2">
         <v>1619</v>
-      </c>
-      <c r="C761" t="s" s="2">
-        <v>1620</v>
       </c>
       <c r="D761" s="2"/>
     </row>
@@ -16383,10 +16404,10 @@
         <v>96</v>
       </c>
       <c r="B762" t="s" s="2">
+        <v>1620</v>
+      </c>
+      <c r="C762" t="s" s="2">
         <v>1621</v>
-      </c>
-      <c r="C762" t="s" s="2">
-        <v>1622</v>
       </c>
       <c r="D762" s="2"/>
     </row>
@@ -16395,10 +16416,10 @@
         <v>96</v>
       </c>
       <c r="B763" t="s" s="2">
+        <v>1622</v>
+      </c>
+      <c r="C763" t="s" s="2">
         <v>1623</v>
-      </c>
-      <c r="C763" t="s" s="2">
-        <v>1624</v>
       </c>
       <c r="D763" s="2"/>
     </row>
@@ -16407,10 +16428,10 @@
         <v>96</v>
       </c>
       <c r="B764" t="s" s="2">
+        <v>1624</v>
+      </c>
+      <c r="C764" t="s" s="2">
         <v>1625</v>
-      </c>
-      <c r="C764" t="s" s="2">
-        <v>1626</v>
       </c>
       <c r="D764" s="2"/>
     </row>
@@ -16419,10 +16440,10 @@
         <v>96</v>
       </c>
       <c r="B765" t="s" s="2">
+        <v>1626</v>
+      </c>
+      <c r="C765" t="s" s="2">
         <v>1627</v>
-      </c>
-      <c r="C765" t="s" s="2">
-        <v>1628</v>
       </c>
       <c r="D765" s="2"/>
     </row>
@@ -16431,10 +16452,10 @@
         <v>96</v>
       </c>
       <c r="B766" t="s" s="2">
+        <v>1628</v>
+      </c>
+      <c r="C766" t="s" s="2">
         <v>1629</v>
-      </c>
-      <c r="C766" t="s" s="2">
-        <v>1630</v>
       </c>
       <c r="D766" s="2"/>
     </row>
@@ -16443,10 +16464,10 @@
         <v>96</v>
       </c>
       <c r="B767" t="s" s="2">
+        <v>1630</v>
+      </c>
+      <c r="C767" t="s" s="2">
         <v>1631</v>
-      </c>
-      <c r="C767" t="s" s="2">
-        <v>1632</v>
       </c>
       <c r="D767" s="2"/>
     </row>
@@ -16455,10 +16476,10 @@
         <v>96</v>
       </c>
       <c r="B768" t="s" s="2">
+        <v>1632</v>
+      </c>
+      <c r="C768" t="s" s="2">
         <v>1633</v>
-      </c>
-      <c r="C768" t="s" s="2">
-        <v>1634</v>
       </c>
       <c r="D768" s="2"/>
     </row>
@@ -16467,10 +16488,10 @@
         <v>96</v>
       </c>
       <c r="B769" t="s" s="2">
+        <v>1634</v>
+      </c>
+      <c r="C769" t="s" s="2">
         <v>1635</v>
-      </c>
-      <c r="C769" t="s" s="2">
-        <v>1636</v>
       </c>
       <c r="D769" s="2"/>
     </row>
@@ -16479,10 +16500,10 @@
         <v>96</v>
       </c>
       <c r="B770" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="C770" t="s" s="2">
         <v>1637</v>
-      </c>
-      <c r="C770" t="s" s="2">
-        <v>1638</v>
       </c>
       <c r="D770" s="2"/>
     </row>
@@ -16491,10 +16512,10 @@
         <v>96</v>
       </c>
       <c r="B771" t="s" s="2">
+        <v>1638</v>
+      </c>
+      <c r="C771" t="s" s="2">
         <v>1639</v>
-      </c>
-      <c r="C771" t="s" s="2">
-        <v>1640</v>
       </c>
       <c r="D771" s="2"/>
     </row>
@@ -16503,10 +16524,10 @@
         <v>96</v>
       </c>
       <c r="B772" t="s" s="2">
+        <v>1640</v>
+      </c>
+      <c r="C772" t="s" s="2">
         <v>1641</v>
-      </c>
-      <c r="C772" t="s" s="2">
-        <v>1642</v>
       </c>
       <c r="D772" s="2"/>
     </row>
@@ -16515,10 +16536,10 @@
         <v>96</v>
       </c>
       <c r="B773" t="s" s="2">
+        <v>1642</v>
+      </c>
+      <c r="C773" t="s" s="2">
         <v>1643</v>
-      </c>
-      <c r="C773" t="s" s="2">
-        <v>1644</v>
       </c>
       <c r="D773" s="2"/>
     </row>
@@ -16527,10 +16548,10 @@
         <v>96</v>
       </c>
       <c r="B774" t="s" s="2">
+        <v>1644</v>
+      </c>
+      <c r="C774" t="s" s="2">
         <v>1645</v>
-      </c>
-      <c r="C774" t="s" s="2">
-        <v>1646</v>
       </c>
       <c r="D774" s="2"/>
     </row>
@@ -16539,10 +16560,10 @@
         <v>96</v>
       </c>
       <c r="B775" t="s" s="2">
+        <v>1646</v>
+      </c>
+      <c r="C775" t="s" s="2">
         <v>1647</v>
-      </c>
-      <c r="C775" t="s" s="2">
-        <v>1648</v>
       </c>
       <c r="D775" s="2"/>
     </row>
@@ -16551,10 +16572,10 @@
         <v>96</v>
       </c>
       <c r="B776" t="s" s="2">
+        <v>1648</v>
+      </c>
+      <c r="C776" t="s" s="2">
         <v>1649</v>
-      </c>
-      <c r="C776" t="s" s="2">
-        <v>1650</v>
       </c>
       <c r="D776" s="2"/>
     </row>
@@ -16563,10 +16584,10 @@
         <v>96</v>
       </c>
       <c r="B777" t="s" s="2">
+        <v>1650</v>
+      </c>
+      <c r="C777" t="s" s="2">
         <v>1651</v>
-      </c>
-      <c r="C777" t="s" s="2">
-        <v>1652</v>
       </c>
       <c r="D777" s="2"/>
     </row>
@@ -16575,10 +16596,10 @@
         <v>96</v>
       </c>
       <c r="B778" t="s" s="2">
+        <v>1652</v>
+      </c>
+      <c r="C778" t="s" s="2">
         <v>1653</v>
-      </c>
-      <c r="C778" t="s" s="2">
-        <v>1654</v>
       </c>
       <c r="D778" s="2"/>
     </row>
@@ -16587,10 +16608,10 @@
         <v>96</v>
       </c>
       <c r="B779" t="s" s="2">
+        <v>1654</v>
+      </c>
+      <c r="C779" t="s" s="2">
         <v>1655</v>
-      </c>
-      <c r="C779" t="s" s="2">
-        <v>1656</v>
       </c>
       <c r="D779" s="2"/>
     </row>
@@ -16599,10 +16620,10 @@
         <v>96</v>
       </c>
       <c r="B780" t="s" s="2">
+        <v>1656</v>
+      </c>
+      <c r="C780" t="s" s="2">
         <v>1657</v>
-      </c>
-      <c r="C780" t="s" s="2">
-        <v>1658</v>
       </c>
       <c r="D780" s="2"/>
     </row>
@@ -16611,10 +16632,10 @@
         <v>96</v>
       </c>
       <c r="B781" t="s" s="2">
+        <v>1658</v>
+      </c>
+      <c r="C781" t="s" s="2">
         <v>1659</v>
-      </c>
-      <c r="C781" t="s" s="2">
-        <v>1660</v>
       </c>
       <c r="D781" s="2"/>
     </row>
@@ -16623,10 +16644,10 @@
         <v>96</v>
       </c>
       <c r="B782" t="s" s="2">
+        <v>1660</v>
+      </c>
+      <c r="C782" t="s" s="2">
         <v>1661</v>
-      </c>
-      <c r="C782" t="s" s="2">
-        <v>1662</v>
       </c>
       <c r="D782" s="2"/>
     </row>
@@ -16635,10 +16656,10 @@
         <v>96</v>
       </c>
       <c r="B783" t="s" s="2">
+        <v>1662</v>
+      </c>
+      <c r="C783" t="s" s="2">
         <v>1663</v>
-      </c>
-      <c r="C783" t="s" s="2">
-        <v>1664</v>
       </c>
       <c r="D783" s="2"/>
     </row>
@@ -16647,10 +16668,10 @@
         <v>96</v>
       </c>
       <c r="B784" t="s" s="2">
+        <v>1664</v>
+      </c>
+      <c r="C784" t="s" s="2">
         <v>1665</v>
-      </c>
-      <c r="C784" t="s" s="2">
-        <v>1666</v>
       </c>
       <c r="D784" s="2"/>
     </row>
@@ -16659,10 +16680,10 @@
         <v>96</v>
       </c>
       <c r="B785" t="s" s="2">
+        <v>1666</v>
+      </c>
+      <c r="C785" t="s" s="2">
         <v>1667</v>
-      </c>
-      <c r="C785" t="s" s="2">
-        <v>1668</v>
       </c>
       <c r="D785" s="2"/>
     </row>
@@ -16671,10 +16692,10 @@
         <v>96</v>
       </c>
       <c r="B786" t="s" s="2">
+        <v>1668</v>
+      </c>
+      <c r="C786" t="s" s="2">
         <v>1669</v>
-      </c>
-      <c r="C786" t="s" s="2">
-        <v>1670</v>
       </c>
       <c r="D786" s="2"/>
     </row>
@@ -16683,10 +16704,10 @@
         <v>96</v>
       </c>
       <c r="B787" t="s" s="2">
+        <v>1670</v>
+      </c>
+      <c r="C787" t="s" s="2">
         <v>1671</v>
-      </c>
-      <c r="C787" t="s" s="2">
-        <v>1672</v>
       </c>
       <c r="D787" s="2"/>
     </row>
@@ -16695,10 +16716,10 @@
         <v>96</v>
       </c>
       <c r="B788" t="s" s="2">
+        <v>1672</v>
+      </c>
+      <c r="C788" t="s" s="2">
         <v>1673</v>
-      </c>
-      <c r="C788" t="s" s="2">
-        <v>1674</v>
       </c>
       <c r="D788" s="2"/>
     </row>
@@ -16707,10 +16728,10 @@
         <v>96</v>
       </c>
       <c r="B789" t="s" s="2">
+        <v>1674</v>
+      </c>
+      <c r="C789" t="s" s="2">
         <v>1675</v>
-      </c>
-      <c r="C789" t="s" s="2">
-        <v>1676</v>
       </c>
       <c r="D789" s="2"/>
     </row>
@@ -16719,10 +16740,10 @@
         <v>96</v>
       </c>
       <c r="B790" t="s" s="2">
+        <v>1676</v>
+      </c>
+      <c r="C790" t="s" s="2">
         <v>1677</v>
-      </c>
-      <c r="C790" t="s" s="2">
-        <v>1678</v>
       </c>
       <c r="D790" s="2"/>
     </row>
@@ -16731,10 +16752,10 @@
         <v>96</v>
       </c>
       <c r="B791" t="s" s="2">
+        <v>1678</v>
+      </c>
+      <c r="C791" t="s" s="2">
         <v>1679</v>
-      </c>
-      <c r="C791" t="s" s="2">
-        <v>1680</v>
       </c>
       <c r="D791" s="2"/>
     </row>
@@ -16743,10 +16764,10 @@
         <v>96</v>
       </c>
       <c r="B792" t="s" s="2">
+        <v>1680</v>
+      </c>
+      <c r="C792" t="s" s="2">
         <v>1681</v>
-      </c>
-      <c r="C792" t="s" s="2">
-        <v>1682</v>
       </c>
       <c r="D792" s="2"/>
     </row>
@@ -16755,10 +16776,10 @@
         <v>96</v>
       </c>
       <c r="B793" t="s" s="2">
+        <v>1682</v>
+      </c>
+      <c r="C793" t="s" s="2">
         <v>1683</v>
-      </c>
-      <c r="C793" t="s" s="2">
-        <v>1684</v>
       </c>
       <c r="D793" s="2"/>
     </row>
@@ -16767,10 +16788,10 @@
         <v>96</v>
       </c>
       <c r="B794" t="s" s="2">
+        <v>1684</v>
+      </c>
+      <c r="C794" t="s" s="2">
         <v>1685</v>
-      </c>
-      <c r="C794" t="s" s="2">
-        <v>1686</v>
       </c>
       <c r="D794" s="2"/>
     </row>
@@ -16779,10 +16800,10 @@
         <v>96</v>
       </c>
       <c r="B795" t="s" s="2">
+        <v>1686</v>
+      </c>
+      <c r="C795" t="s" s="2">
         <v>1687</v>
-      </c>
-      <c r="C795" t="s" s="2">
-        <v>1688</v>
       </c>
       <c r="D795" s="2"/>
     </row>
@@ -16791,10 +16812,10 @@
         <v>96</v>
       </c>
       <c r="B796" t="s" s="2">
+        <v>1688</v>
+      </c>
+      <c r="C796" t="s" s="2">
         <v>1689</v>
-      </c>
-      <c r="C796" t="s" s="2">
-        <v>1690</v>
       </c>
       <c r="D796" s="2"/>
     </row>
@@ -16803,10 +16824,10 @@
         <v>96</v>
       </c>
       <c r="B797" t="s" s="2">
+        <v>1690</v>
+      </c>
+      <c r="C797" t="s" s="2">
         <v>1691</v>
-      </c>
-      <c r="C797" t="s" s="2">
-        <v>1692</v>
       </c>
       <c r="D797" s="2"/>
     </row>
@@ -16815,24 +16836,22 @@
         <v>96</v>
       </c>
       <c r="B798" t="s" s="2">
+        <v>1692</v>
+      </c>
+      <c r="C798" t="s" s="2">
         <v>1693</v>
       </c>
-      <c r="C798" t="s" s="2">
-        <v>1694</v>
-      </c>
-      <c r="D798" t="s" s="2">
-        <v>1695</v>
-      </c>
+      <c r="D798" s="2"/>
     </row>
     <row r="799">
       <c r="A799" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B799" t="s" s="2">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="C799" t="s" s="2">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="D799" s="2"/>
     </row>
@@ -16841,22 +16860,24 @@
         <v>96</v>
       </c>
       <c r="B800" t="s" s="2">
+        <v>1696</v>
+      </c>
+      <c r="C800" t="s" s="2">
+        <v>1697</v>
+      </c>
+      <c r="D800" t="s" s="2">
         <v>1698</v>
       </c>
-      <c r="C800" t="s" s="2">
-        <v>1699</v>
-      </c>
-      <c r="D800" s="2"/>
     </row>
     <row r="801">
       <c r="A801" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B801" t="s" s="2">
+        <v>1699</v>
+      </c>
+      <c r="C801" t="s" s="2">
         <v>1700</v>
-      </c>
-      <c r="C801" t="s" s="2">
-        <v>1701</v>
       </c>
       <c r="D801" s="2"/>
     </row>
@@ -16865,10 +16886,10 @@
         <v>96</v>
       </c>
       <c r="B802" t="s" s="2">
+        <v>1701</v>
+      </c>
+      <c r="C802" t="s" s="2">
         <v>1702</v>
-      </c>
-      <c r="C802" t="s" s="2">
-        <v>1703</v>
       </c>
       <c r="D802" s="2"/>
     </row>
@@ -16877,10 +16898,10 @@
         <v>96</v>
       </c>
       <c r="B803" t="s" s="2">
+        <v>1703</v>
+      </c>
+      <c r="C803" t="s" s="2">
         <v>1704</v>
-      </c>
-      <c r="C803" t="s" s="2">
-        <v>1705</v>
       </c>
       <c r="D803" s="2"/>
     </row>
@@ -16889,10 +16910,10 @@
         <v>96</v>
       </c>
       <c r="B804" t="s" s="2">
+        <v>1705</v>
+      </c>
+      <c r="C804" t="s" s="2">
         <v>1706</v>
-      </c>
-      <c r="C804" t="s" s="2">
-        <v>1707</v>
       </c>
       <c r="D804" s="2"/>
     </row>
@@ -16901,10 +16922,10 @@
         <v>96</v>
       </c>
       <c r="B805" t="s" s="2">
+        <v>1707</v>
+      </c>
+      <c r="C805" t="s" s="2">
         <v>1708</v>
-      </c>
-      <c r="C805" t="s" s="2">
-        <v>1709</v>
       </c>
       <c r="D805" s="2"/>
     </row>
@@ -16913,10 +16934,10 @@
         <v>96</v>
       </c>
       <c r="B806" t="s" s="2">
+        <v>1709</v>
+      </c>
+      <c r="C806" t="s" s="2">
         <v>1710</v>
-      </c>
-      <c r="C806" t="s" s="2">
-        <v>1711</v>
       </c>
       <c r="D806" s="2"/>
     </row>
@@ -16925,10 +16946,10 @@
         <v>96</v>
       </c>
       <c r="B807" t="s" s="2">
+        <v>1711</v>
+      </c>
+      <c r="C807" t="s" s="2">
         <v>1712</v>
-      </c>
-      <c r="C807" t="s" s="2">
-        <v>1713</v>
       </c>
       <c r="D807" s="2"/>
     </row>
@@ -16937,10 +16958,10 @@
         <v>96</v>
       </c>
       <c r="B808" t="s" s="2">
+        <v>1713</v>
+      </c>
+      <c r="C808" t="s" s="2">
         <v>1714</v>
-      </c>
-      <c r="C808" t="s" s="2">
-        <v>1715</v>
       </c>
       <c r="D808" s="2"/>
     </row>
@@ -16949,10 +16970,10 @@
         <v>96</v>
       </c>
       <c r="B809" t="s" s="2">
+        <v>1715</v>
+      </c>
+      <c r="C809" t="s" s="2">
         <v>1716</v>
-      </c>
-      <c r="C809" t="s" s="2">
-        <v>1717</v>
       </c>
       <c r="D809" s="2"/>
     </row>
@@ -16961,10 +16982,10 @@
         <v>96</v>
       </c>
       <c r="B810" t="s" s="2">
+        <v>1717</v>
+      </c>
+      <c r="C810" t="s" s="2">
         <v>1718</v>
-      </c>
-      <c r="C810" t="s" s="2">
-        <v>1719</v>
       </c>
       <c r="D810" s="2"/>
     </row>
@@ -16973,10 +16994,10 @@
         <v>96</v>
       </c>
       <c r="B811" t="s" s="2">
+        <v>1719</v>
+      </c>
+      <c r="C811" t="s" s="2">
         <v>1720</v>
-      </c>
-      <c r="C811" t="s" s="2">
-        <v>1721</v>
       </c>
       <c r="D811" s="2"/>
     </row>
@@ -16985,10 +17006,10 @@
         <v>96</v>
       </c>
       <c r="B812" t="s" s="2">
+        <v>1721</v>
+      </c>
+      <c r="C812" t="s" s="2">
         <v>1722</v>
-      </c>
-      <c r="C812" t="s" s="2">
-        <v>1723</v>
       </c>
       <c r="D812" s="2"/>
     </row>
@@ -16997,10 +17018,10 @@
         <v>96</v>
       </c>
       <c r="B813" t="s" s="2">
+        <v>1723</v>
+      </c>
+      <c r="C813" t="s" s="2">
         <v>1724</v>
-      </c>
-      <c r="C813" t="s" s="2">
-        <v>1725</v>
       </c>
       <c r="D813" s="2"/>
     </row>
@@ -17009,24 +17030,22 @@
         <v>96</v>
       </c>
       <c r="B814" t="s" s="2">
+        <v>1725</v>
+      </c>
+      <c r="C814" t="s" s="2">
         <v>1726</v>
       </c>
-      <c r="C814" t="s" s="2">
-        <v>1727</v>
-      </c>
-      <c r="D814" t="s" s="2">
-        <v>1728</v>
-      </c>
+      <c r="D814" s="2"/>
     </row>
     <row r="815">
       <c r="A815" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B815" t="s" s="2">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="C815" t="s" s="2">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D815" s="2"/>
     </row>
@@ -17035,22 +17054,24 @@
         <v>96</v>
       </c>
       <c r="B816" t="s" s="2">
+        <v>1729</v>
+      </c>
+      <c r="C816" t="s" s="2">
+        <v>1730</v>
+      </c>
+      <c r="D816" t="s" s="2">
         <v>1731</v>
       </c>
-      <c r="C816" t="s" s="2">
-        <v>1732</v>
-      </c>
-      <c r="D816" s="2"/>
     </row>
     <row r="817">
       <c r="A817" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B817" t="s" s="2">
+        <v>1732</v>
+      </c>
+      <c r="C817" t="s" s="2">
         <v>1733</v>
-      </c>
-      <c r="C817" t="s" s="2">
-        <v>1734</v>
       </c>
       <c r="D817" s="2"/>
     </row>
@@ -17059,10 +17080,10 @@
         <v>96</v>
       </c>
       <c r="B818" t="s" s="2">
+        <v>1734</v>
+      </c>
+      <c r="C818" t="s" s="2">
         <v>1735</v>
-      </c>
-      <c r="C818" t="s" s="2">
-        <v>1736</v>
       </c>
       <c r="D818" s="2"/>
     </row>
@@ -17071,10 +17092,10 @@
         <v>96</v>
       </c>
       <c r="B819" t="s" s="2">
+        <v>1736</v>
+      </c>
+      <c r="C819" t="s" s="2">
         <v>1737</v>
-      </c>
-      <c r="C819" t="s" s="2">
-        <v>1738</v>
       </c>
       <c r="D819" s="2"/>
     </row>
@@ -17083,7 +17104,7 @@
         <v>96</v>
       </c>
       <c r="B820" t="s" s="2">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="C820" t="s" s="2">
         <v>1739</v>
@@ -17110,7 +17131,7 @@
         <v>1742</v>
       </c>
       <c r="C822" t="s" s="2">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="D822" s="2"/>
     </row>
@@ -17119,10 +17140,10 @@
         <v>96</v>
       </c>
       <c r="B823" t="s" s="2">
+        <v>1743</v>
+      </c>
+      <c r="C823" t="s" s="2">
         <v>1744</v>
-      </c>
-      <c r="C823" t="s" s="2">
-        <v>1745</v>
       </c>
       <c r="D823" s="2"/>
     </row>
@@ -17131,10 +17152,10 @@
         <v>96</v>
       </c>
       <c r="B824" t="s" s="2">
+        <v>1745</v>
+      </c>
+      <c r="C824" t="s" s="2">
         <v>1746</v>
-      </c>
-      <c r="C824" t="s" s="2">
-        <v>1747</v>
       </c>
       <c r="D824" s="2"/>
     </row>
@@ -17143,10 +17164,10 @@
         <v>96</v>
       </c>
       <c r="B825" t="s" s="2">
+        <v>1747</v>
+      </c>
+      <c r="C825" t="s" s="2">
         <v>1748</v>
-      </c>
-      <c r="C825" t="s" s="2">
-        <v>1749</v>
       </c>
       <c r="D825" s="2"/>
     </row>
@@ -17155,10 +17176,10 @@
         <v>96</v>
       </c>
       <c r="B826" t="s" s="2">
+        <v>1749</v>
+      </c>
+      <c r="C826" t="s" s="2">
         <v>1750</v>
-      </c>
-      <c r="C826" t="s" s="2">
-        <v>1751</v>
       </c>
       <c r="D826" s="2"/>
     </row>
@@ -17167,10 +17188,10 @@
         <v>96</v>
       </c>
       <c r="B827" t="s" s="2">
+        <v>1751</v>
+      </c>
+      <c r="C827" t="s" s="2">
         <v>1752</v>
-      </c>
-      <c r="C827" t="s" s="2">
-        <v>1753</v>
       </c>
       <c r="D827" s="2"/>
     </row>
@@ -17179,10 +17200,10 @@
         <v>96</v>
       </c>
       <c r="B828" t="s" s="2">
+        <v>1753</v>
+      </c>
+      <c r="C828" t="s" s="2">
         <v>1754</v>
-      </c>
-      <c r="C828" t="s" s="2">
-        <v>1755</v>
       </c>
       <c r="D828" s="2"/>
     </row>
@@ -17191,10 +17212,10 @@
         <v>96</v>
       </c>
       <c r="B829" t="s" s="2">
+        <v>1755</v>
+      </c>
+      <c r="C829" t="s" s="2">
         <v>1756</v>
-      </c>
-      <c r="C829" t="s" s="2">
-        <v>1757</v>
       </c>
       <c r="D829" s="2"/>
     </row>
@@ -17203,10 +17224,10 @@
         <v>96</v>
       </c>
       <c r="B830" t="s" s="2">
+        <v>1757</v>
+      </c>
+      <c r="C830" t="s" s="2">
         <v>1758</v>
-      </c>
-      <c r="C830" t="s" s="2">
-        <v>1759</v>
       </c>
       <c r="D830" s="2"/>
     </row>
@@ -17215,10 +17236,10 @@
         <v>96</v>
       </c>
       <c r="B831" t="s" s="2">
+        <v>1759</v>
+      </c>
+      <c r="C831" t="s" s="2">
         <v>1760</v>
-      </c>
-      <c r="C831" t="s" s="2">
-        <v>1761</v>
       </c>
       <c r="D831" s="2"/>
     </row>
@@ -17227,10 +17248,10 @@
         <v>96</v>
       </c>
       <c r="B832" t="s" s="2">
+        <v>1761</v>
+      </c>
+      <c r="C832" t="s" s="2">
         <v>1762</v>
-      </c>
-      <c r="C832" t="s" s="2">
-        <v>1763</v>
       </c>
       <c r="D832" s="2"/>
     </row>
@@ -17239,10 +17260,10 @@
         <v>96</v>
       </c>
       <c r="B833" t="s" s="2">
+        <v>1763</v>
+      </c>
+      <c r="C833" t="s" s="2">
         <v>1764</v>
-      </c>
-      <c r="C833" t="s" s="2">
-        <v>1765</v>
       </c>
       <c r="D833" s="2"/>
     </row>
@@ -17251,10 +17272,10 @@
         <v>96</v>
       </c>
       <c r="B834" t="s" s="2">
+        <v>1765</v>
+      </c>
+      <c r="C834" t="s" s="2">
         <v>1766</v>
-      </c>
-      <c r="C834" t="s" s="2">
-        <v>1767</v>
       </c>
       <c r="D834" s="2"/>
     </row>
@@ -17263,10 +17284,10 @@
         <v>96</v>
       </c>
       <c r="B835" t="s" s="2">
+        <v>1767</v>
+      </c>
+      <c r="C835" t="s" s="2">
         <v>1768</v>
-      </c>
-      <c r="C835" t="s" s="2">
-        <v>1769</v>
       </c>
       <c r="D835" s="2"/>
     </row>
@@ -17275,10 +17296,10 @@
         <v>96</v>
       </c>
       <c r="B836" t="s" s="2">
+        <v>1769</v>
+      </c>
+      <c r="C836" t="s" s="2">
         <v>1770</v>
-      </c>
-      <c r="C836" t="s" s="2">
-        <v>1771</v>
       </c>
       <c r="D836" s="2"/>
     </row>
@@ -17287,10 +17308,10 @@
         <v>96</v>
       </c>
       <c r="B837" t="s" s="2">
+        <v>1771</v>
+      </c>
+      <c r="C837" t="s" s="2">
         <v>1772</v>
-      </c>
-      <c r="C837" t="s" s="2">
-        <v>1773</v>
       </c>
       <c r="D837" s="2"/>
     </row>
@@ -17299,10 +17320,10 @@
         <v>96</v>
       </c>
       <c r="B838" t="s" s="2">
+        <v>1773</v>
+      </c>
+      <c r="C838" t="s" s="2">
         <v>1774</v>
-      </c>
-      <c r="C838" t="s" s="2">
-        <v>1775</v>
       </c>
       <c r="D838" s="2"/>
     </row>
@@ -17311,10 +17332,10 @@
         <v>96</v>
       </c>
       <c r="B839" t="s" s="2">
+        <v>1775</v>
+      </c>
+      <c r="C839" t="s" s="2">
         <v>1776</v>
-      </c>
-      <c r="C839" t="s" s="2">
-        <v>1777</v>
       </c>
       <c r="D839" s="2"/>
     </row>
@@ -17323,10 +17344,10 @@
         <v>96</v>
       </c>
       <c r="B840" t="s" s="2">
+        <v>1777</v>
+      </c>
+      <c r="C840" t="s" s="2">
         <v>1778</v>
-      </c>
-      <c r="C840" t="s" s="2">
-        <v>1779</v>
       </c>
       <c r="D840" s="2"/>
     </row>
@@ -17335,10 +17356,10 @@
         <v>96</v>
       </c>
       <c r="B841" t="s" s="2">
+        <v>1779</v>
+      </c>
+      <c r="C841" t="s" s="2">
         <v>1780</v>
-      </c>
-      <c r="C841" t="s" s="2">
-        <v>1781</v>
       </c>
       <c r="D841" s="2"/>
     </row>
@@ -17347,10 +17368,10 @@
         <v>96</v>
       </c>
       <c r="B842" t="s" s="2">
+        <v>1781</v>
+      </c>
+      <c r="C842" t="s" s="2">
         <v>1782</v>
-      </c>
-      <c r="C842" t="s" s="2">
-        <v>1783</v>
       </c>
       <c r="D842" s="2"/>
     </row>
@@ -17359,10 +17380,10 @@
         <v>96</v>
       </c>
       <c r="B843" t="s" s="2">
+        <v>1783</v>
+      </c>
+      <c r="C843" t="s" s="2">
         <v>1784</v>
-      </c>
-      <c r="C843" t="s" s="2">
-        <v>1785</v>
       </c>
       <c r="D843" s="2"/>
     </row>
@@ -17371,10 +17392,10 @@
         <v>96</v>
       </c>
       <c r="B844" t="s" s="2">
+        <v>1785</v>
+      </c>
+      <c r="C844" t="s" s="2">
         <v>1786</v>
-      </c>
-      <c r="C844" t="s" s="2">
-        <v>1787</v>
       </c>
       <c r="D844" s="2"/>
     </row>
@@ -17383,10 +17404,10 @@
         <v>96</v>
       </c>
       <c r="B845" t="s" s="2">
+        <v>1787</v>
+      </c>
+      <c r="C845" t="s" s="2">
         <v>1788</v>
-      </c>
-      <c r="C845" t="s" s="2">
-        <v>1789</v>
       </c>
       <c r="D845" s="2"/>
     </row>
@@ -17395,10 +17416,10 @@
         <v>96</v>
       </c>
       <c r="B846" t="s" s="2">
+        <v>1789</v>
+      </c>
+      <c r="C846" t="s" s="2">
         <v>1790</v>
-      </c>
-      <c r="C846" t="s" s="2">
-        <v>1791</v>
       </c>
       <c r="D846" s="2"/>
     </row>
@@ -17407,10 +17428,10 @@
         <v>96</v>
       </c>
       <c r="B847" t="s" s="2">
+        <v>1791</v>
+      </c>
+      <c r="C847" t="s" s="2">
         <v>1792</v>
-      </c>
-      <c r="C847" t="s" s="2">
-        <v>1793</v>
       </c>
       <c r="D847" s="2"/>
     </row>
@@ -17419,10 +17440,10 @@
         <v>96</v>
       </c>
       <c r="B848" t="s" s="2">
+        <v>1793</v>
+      </c>
+      <c r="C848" t="s" s="2">
         <v>1794</v>
-      </c>
-      <c r="C848" t="s" s="2">
-        <v>1795</v>
       </c>
       <c r="D848" s="2"/>
     </row>
@@ -17431,10 +17452,10 @@
         <v>96</v>
       </c>
       <c r="B849" t="s" s="2">
+        <v>1795</v>
+      </c>
+      <c r="C849" t="s" s="2">
         <v>1796</v>
-      </c>
-      <c r="C849" t="s" s="2">
-        <v>1797</v>
       </c>
       <c r="D849" s="2"/>
     </row>
@@ -17443,10 +17464,10 @@
         <v>96</v>
       </c>
       <c r="B850" t="s" s="2">
+        <v>1797</v>
+      </c>
+      <c r="C850" t="s" s="2">
         <v>1798</v>
-      </c>
-      <c r="C850" t="s" s="2">
-        <v>1799</v>
       </c>
       <c r="D850" s="2"/>
     </row>
@@ -17455,10 +17476,10 @@
         <v>96</v>
       </c>
       <c r="B851" t="s" s="2">
+        <v>1799</v>
+      </c>
+      <c r="C851" t="s" s="2">
         <v>1800</v>
-      </c>
-      <c r="C851" t="s" s="2">
-        <v>1801</v>
       </c>
       <c r="D851" s="2"/>
     </row>
@@ -17467,10 +17488,10 @@
         <v>96</v>
       </c>
       <c r="B852" t="s" s="2">
+        <v>1801</v>
+      </c>
+      <c r="C852" t="s" s="2">
         <v>1802</v>
-      </c>
-      <c r="C852" t="s" s="2">
-        <v>1803</v>
       </c>
       <c r="D852" s="2"/>
     </row>
@@ -17479,10 +17500,10 @@
         <v>96</v>
       </c>
       <c r="B853" t="s" s="2">
+        <v>1803</v>
+      </c>
+      <c r="C853" t="s" s="2">
         <v>1804</v>
-      </c>
-      <c r="C853" t="s" s="2">
-        <v>1805</v>
       </c>
       <c r="D853" s="2"/>
     </row>
@@ -17491,10 +17512,10 @@
         <v>96</v>
       </c>
       <c r="B854" t="s" s="2">
+        <v>1805</v>
+      </c>
+      <c r="C854" t="s" s="2">
         <v>1806</v>
-      </c>
-      <c r="C854" t="s" s="2">
-        <v>1807</v>
       </c>
       <c r="D854" s="2"/>
     </row>
@@ -17503,10 +17524,10 @@
         <v>96</v>
       </c>
       <c r="B855" t="s" s="2">
+        <v>1807</v>
+      </c>
+      <c r="C855" t="s" s="2">
         <v>1808</v>
-      </c>
-      <c r="C855" t="s" s="2">
-        <v>1809</v>
       </c>
       <c r="D855" s="2"/>
     </row>
@@ -17515,10 +17536,10 @@
         <v>96</v>
       </c>
       <c r="B856" t="s" s="2">
+        <v>1809</v>
+      </c>
+      <c r="C856" t="s" s="2">
         <v>1810</v>
-      </c>
-      <c r="C856" t="s" s="2">
-        <v>1811</v>
       </c>
       <c r="D856" s="2"/>
     </row>
@@ -17527,10 +17548,10 @@
         <v>96</v>
       </c>
       <c r="B857" t="s" s="2">
+        <v>1811</v>
+      </c>
+      <c r="C857" t="s" s="2">
         <v>1812</v>
-      </c>
-      <c r="C857" t="s" s="2">
-        <v>1813</v>
       </c>
       <c r="D857" s="2"/>
     </row>
@@ -17539,10 +17560,10 @@
         <v>96</v>
       </c>
       <c r="B858" t="s" s="2">
+        <v>1813</v>
+      </c>
+      <c r="C858" t="s" s="2">
         <v>1814</v>
-      </c>
-      <c r="C858" t="s" s="2">
-        <v>1815</v>
       </c>
       <c r="D858" s="2"/>
     </row>
@@ -17551,10 +17572,10 @@
         <v>96</v>
       </c>
       <c r="B859" t="s" s="2">
+        <v>1815</v>
+      </c>
+      <c r="C859" t="s" s="2">
         <v>1816</v>
-      </c>
-      <c r="C859" t="s" s="2">
-        <v>1817</v>
       </c>
       <c r="D859" s="2"/>
     </row>
@@ -17563,10 +17584,10 @@
         <v>96</v>
       </c>
       <c r="B860" t="s" s="2">
+        <v>1817</v>
+      </c>
+      <c r="C860" t="s" s="2">
         <v>1818</v>
-      </c>
-      <c r="C860" t="s" s="2">
-        <v>1819</v>
       </c>
       <c r="D860" s="2"/>
     </row>
@@ -17575,10 +17596,10 @@
         <v>96</v>
       </c>
       <c r="B861" t="s" s="2">
+        <v>1819</v>
+      </c>
+      <c r="C861" t="s" s="2">
         <v>1820</v>
-      </c>
-      <c r="C861" t="s" s="2">
-        <v>1821</v>
       </c>
       <c r="D861" s="2"/>
     </row>
@@ -17587,10 +17608,10 @@
         <v>96</v>
       </c>
       <c r="B862" t="s" s="2">
+        <v>1821</v>
+      </c>
+      <c r="C862" t="s" s="2">
         <v>1822</v>
-      </c>
-      <c r="C862" t="s" s="2">
-        <v>1823</v>
       </c>
       <c r="D862" s="2"/>
     </row>
@@ -17599,24 +17620,22 @@
         <v>96</v>
       </c>
       <c r="B863" t="s" s="2">
+        <v>1823</v>
+      </c>
+      <c r="C863" t="s" s="2">
         <v>1824</v>
       </c>
-      <c r="C863" t="s" s="2">
-        <v>1825</v>
-      </c>
-      <c r="D863" t="s" s="2">
-        <v>1826</v>
-      </c>
+      <c r="D863" s="2"/>
     </row>
     <row r="864">
       <c r="A864" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B864" t="s" s="2">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="C864" t="s" s="2">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="D864" s="2"/>
     </row>
@@ -17625,22 +17644,24 @@
         <v>96</v>
       </c>
       <c r="B865" t="s" s="2">
+        <v>1827</v>
+      </c>
+      <c r="C865" t="s" s="2">
+        <v>1828</v>
+      </c>
+      <c r="D865" t="s" s="2">
         <v>1829</v>
       </c>
-      <c r="C865" t="s" s="2">
-        <v>1830</v>
-      </c>
-      <c r="D865" s="2"/>
     </row>
     <row r="866">
       <c r="A866" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B866" t="s" s="2">
+        <v>1830</v>
+      </c>
+      <c r="C866" t="s" s="2">
         <v>1831</v>
-      </c>
-      <c r="C866" t="s" s="2">
-        <v>1832</v>
       </c>
       <c r="D866" s="2"/>
     </row>
@@ -17649,10 +17670,10 @@
         <v>96</v>
       </c>
       <c r="B867" t="s" s="2">
+        <v>1832</v>
+      </c>
+      <c r="C867" t="s" s="2">
         <v>1833</v>
-      </c>
-      <c r="C867" t="s" s="2">
-        <v>1834</v>
       </c>
       <c r="D867" s="2"/>
     </row>
@@ -17661,10 +17682,10 @@
         <v>96</v>
       </c>
       <c r="B868" t="s" s="2">
+        <v>1834</v>
+      </c>
+      <c r="C868" t="s" s="2">
         <v>1835</v>
-      </c>
-      <c r="C868" t="s" s="2">
-        <v>1836</v>
       </c>
       <c r="D868" s="2"/>
     </row>
@@ -17673,10 +17694,10 @@
         <v>96</v>
       </c>
       <c r="B869" t="s" s="2">
+        <v>1836</v>
+      </c>
+      <c r="C869" t="s" s="2">
         <v>1837</v>
-      </c>
-      <c r="C869" t="s" s="2">
-        <v>1838</v>
       </c>
       <c r="D869" s="2"/>
     </row>
@@ -17685,10 +17706,10 @@
         <v>96</v>
       </c>
       <c r="B870" t="s" s="2">
+        <v>1838</v>
+      </c>
+      <c r="C870" t="s" s="2">
         <v>1839</v>
-      </c>
-      <c r="C870" t="s" s="2">
-        <v>1840</v>
       </c>
       <c r="D870" s="2"/>
     </row>
@@ -17697,10 +17718,10 @@
         <v>96</v>
       </c>
       <c r="B871" t="s" s="2">
+        <v>1840</v>
+      </c>
+      <c r="C871" t="s" s="2">
         <v>1841</v>
-      </c>
-      <c r="C871" t="s" s="2">
-        <v>1842</v>
       </c>
       <c r="D871" s="2"/>
     </row>
@@ -17709,10 +17730,10 @@
         <v>96</v>
       </c>
       <c r="B872" t="s" s="2">
+        <v>1842</v>
+      </c>
+      <c r="C872" t="s" s="2">
         <v>1843</v>
-      </c>
-      <c r="C872" t="s" s="2">
-        <v>1844</v>
       </c>
       <c r="D872" s="2"/>
     </row>
@@ -17721,10 +17742,10 @@
         <v>96</v>
       </c>
       <c r="B873" t="s" s="2">
+        <v>1844</v>
+      </c>
+      <c r="C873" t="s" s="2">
         <v>1845</v>
-      </c>
-      <c r="C873" t="s" s="2">
-        <v>1846</v>
       </c>
       <c r="D873" s="2"/>
     </row>
@@ -17733,10 +17754,10 @@
         <v>96</v>
       </c>
       <c r="B874" t="s" s="2">
+        <v>1846</v>
+      </c>
+      <c r="C874" t="s" s="2">
         <v>1847</v>
-      </c>
-      <c r="C874" t="s" s="2">
-        <v>1848</v>
       </c>
       <c r="D874" s="2"/>
     </row>
@@ -17745,10 +17766,10 @@
         <v>96</v>
       </c>
       <c r="B875" t="s" s="2">
+        <v>1848</v>
+      </c>
+      <c r="C875" t="s" s="2">
         <v>1849</v>
-      </c>
-      <c r="C875" t="s" s="2">
-        <v>1850</v>
       </c>
       <c r="D875" s="2"/>
     </row>
@@ -17757,10 +17778,10 @@
         <v>96</v>
       </c>
       <c r="B876" t="s" s="2">
+        <v>1850</v>
+      </c>
+      <c r="C876" t="s" s="2">
         <v>1851</v>
-      </c>
-      <c r="C876" t="s" s="2">
-        <v>1852</v>
       </c>
       <c r="D876" s="2"/>
     </row>
@@ -17769,10 +17790,10 @@
         <v>96</v>
       </c>
       <c r="B877" t="s" s="2">
+        <v>1852</v>
+      </c>
+      <c r="C877" t="s" s="2">
         <v>1853</v>
-      </c>
-      <c r="C877" t="s" s="2">
-        <v>1854</v>
       </c>
       <c r="D877" s="2"/>
     </row>
@@ -17781,10 +17802,10 @@
         <v>96</v>
       </c>
       <c r="B878" t="s" s="2">
+        <v>1854</v>
+      </c>
+      <c r="C878" t="s" s="2">
         <v>1855</v>
-      </c>
-      <c r="C878" t="s" s="2">
-        <v>1856</v>
       </c>
       <c r="D878" s="2"/>
     </row>
@@ -17793,24 +17814,22 @@
         <v>96</v>
       </c>
       <c r="B879" t="s" s="2">
+        <v>1856</v>
+      </c>
+      <c r="C879" t="s" s="2">
         <v>1857</v>
       </c>
-      <c r="C879" t="s" s="2">
-        <v>1858</v>
-      </c>
-      <c r="D879" t="s" s="2">
-        <v>1859</v>
-      </c>
+      <c r="D879" s="2"/>
     </row>
     <row r="880">
       <c r="A880" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B880" t="s" s="2">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="C880" t="s" s="2">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="D880" s="2"/>
     </row>
@@ -17819,22 +17838,24 @@
         <v>96</v>
       </c>
       <c r="B881" t="s" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C881" t="s" s="2">
+        <v>1861</v>
+      </c>
+      <c r="D881" t="s" s="2">
         <v>1862</v>
       </c>
-      <c r="C881" t="s" s="2">
-        <v>1863</v>
-      </c>
-      <c r="D881" s="2"/>
     </row>
     <row r="882">
       <c r="A882" t="s" s="2">
         <v>96</v>
       </c>
       <c r="B882" t="s" s="2">
+        <v>1863</v>
+      </c>
+      <c r="C882" t="s" s="2">
         <v>1864</v>
-      </c>
-      <c r="C882" t="s" s="2">
-        <v>1865</v>
       </c>
       <c r="D882" s="2"/>
     </row>
@@ -17843,10 +17864,10 @@
         <v>96</v>
       </c>
       <c r="B883" t="s" s="2">
+        <v>1865</v>
+      </c>
+      <c r="C883" t="s" s="2">
         <v>1866</v>
-      </c>
-      <c r="C883" t="s" s="2">
-        <v>1867</v>
       </c>
       <c r="D883" s="2"/>
     </row>
@@ -17855,10 +17876,10 @@
         <v>96</v>
       </c>
       <c r="B884" t="s" s="2">
+        <v>1867</v>
+      </c>
+      <c r="C884" t="s" s="2">
         <v>1868</v>
-      </c>
-      <c r="C884" t="s" s="2">
-        <v>1869</v>
       </c>
       <c r="D884" s="2"/>
     </row>
@@ -17867,10 +17888,10 @@
         <v>96</v>
       </c>
       <c r="B885" t="s" s="2">
+        <v>1869</v>
+      </c>
+      <c r="C885" t="s" s="2">
         <v>1870</v>
-      </c>
-      <c r="C885" t="s" s="2">
-        <v>1871</v>
       </c>
       <c r="D885" s="2"/>
     </row>
@@ -17879,10 +17900,10 @@
         <v>96</v>
       </c>
       <c r="B886" t="s" s="2">
+        <v>1871</v>
+      </c>
+      <c r="C886" t="s" s="2">
         <v>1872</v>
-      </c>
-      <c r="C886" t="s" s="2">
-        <v>1873</v>
       </c>
       <c r="D886" s="2"/>
     </row>
@@ -17891,10 +17912,10 @@
         <v>96</v>
       </c>
       <c r="B887" t="s" s="2">
+        <v>1873</v>
+      </c>
+      <c r="C887" t="s" s="2">
         <v>1874</v>
-      </c>
-      <c r="C887" t="s" s="2">
-        <v>1875</v>
       </c>
       <c r="D887" s="2"/>
     </row>
@@ -17903,10 +17924,10 @@
         <v>96</v>
       </c>
       <c r="B888" t="s" s="2">
+        <v>1875</v>
+      </c>
+      <c r="C888" t="s" s="2">
         <v>1876</v>
-      </c>
-      <c r="C888" t="s" s="2">
-        <v>1877</v>
       </c>
       <c r="D888" s="2"/>
     </row>
@@ -17915,10 +17936,10 @@
         <v>96</v>
       </c>
       <c r="B889" t="s" s="2">
+        <v>1877</v>
+      </c>
+      <c r="C889" t="s" s="2">
         <v>1878</v>
-      </c>
-      <c r="C889" t="s" s="2">
-        <v>1879</v>
       </c>
       <c r="D889" s="2"/>
     </row>
@@ -17927,10 +17948,10 @@
         <v>96</v>
       </c>
       <c r="B890" t="s" s="2">
+        <v>1879</v>
+      </c>
+      <c r="C890" t="s" s="2">
         <v>1880</v>
-      </c>
-      <c r="C890" t="s" s="2">
-        <v>1881</v>
       </c>
       <c r="D890" s="2"/>
     </row>
@@ -17939,10 +17960,10 @@
         <v>96</v>
       </c>
       <c r="B891" t="s" s="2">
+        <v>1881</v>
+      </c>
+      <c r="C891" t="s" s="2">
         <v>1882</v>
-      </c>
-      <c r="C891" t="s" s="2">
-        <v>1883</v>
       </c>
       <c r="D891" s="2"/>
     </row>
@@ -17951,10 +17972,10 @@
         <v>96</v>
       </c>
       <c r="B892" t="s" s="2">
+        <v>1883</v>
+      </c>
+      <c r="C892" t="s" s="2">
         <v>1884</v>
-      </c>
-      <c r="C892" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="D892" s="2"/>
     </row>
@@ -17978,7 +17999,7 @@
         <v>1887</v>
       </c>
       <c r="C894" t="s" s="2">
-        <v>1888</v>
+        <v>894</v>
       </c>
       <c r="D894" s="2"/>
     </row>
@@ -17987,10 +18008,10 @@
         <v>96</v>
       </c>
       <c r="B895" t="s" s="2">
+        <v>1888</v>
+      </c>
+      <c r="C895" t="s" s="2">
         <v>1889</v>
-      </c>
-      <c r="C895" t="s" s="2">
-        <v>1890</v>
       </c>
       <c r="D895" s="2"/>
     </row>
@@ -17999,10 +18020,10 @@
         <v>96</v>
       </c>
       <c r="B896" t="s" s="2">
+        <v>1890</v>
+      </c>
+      <c r="C896" t="s" s="2">
         <v>1891</v>
-      </c>
-      <c r="C896" t="s" s="2">
-        <v>1892</v>
       </c>
       <c r="D896" s="2"/>
     </row>
@@ -18011,10 +18032,10 @@
         <v>96</v>
       </c>
       <c r="B897" t="s" s="2">
+        <v>1892</v>
+      </c>
+      <c r="C897" t="s" s="2">
         <v>1893</v>
-      </c>
-      <c r="C897" t="s" s="2">
-        <v>1894</v>
       </c>
       <c r="D897" s="2"/>
     </row>
@@ -18023,10 +18044,10 @@
         <v>96</v>
       </c>
       <c r="B898" t="s" s="2">
+        <v>1894</v>
+      </c>
+      <c r="C898" t="s" s="2">
         <v>1895</v>
-      </c>
-      <c r="C898" t="s" s="2">
-        <v>1896</v>
       </c>
       <c r="D898" s="2"/>
     </row>
@@ -18035,10 +18056,10 @@
         <v>96</v>
       </c>
       <c r="B899" t="s" s="2">
+        <v>1896</v>
+      </c>
+      <c r="C899" t="s" s="2">
         <v>1897</v>
-      </c>
-      <c r="C899" t="s" s="2">
-        <v>1898</v>
       </c>
       <c r="D899" s="2"/>
     </row>
@@ -18047,10 +18068,10 @@
         <v>96</v>
       </c>
       <c r="B900" t="s" s="2">
+        <v>1898</v>
+      </c>
+      <c r="C900" t="s" s="2">
         <v>1899</v>
-      </c>
-      <c r="C900" t="s" s="2">
-        <v>1900</v>
       </c>
       <c r="D900" s="2"/>
     </row>
@@ -18059,10 +18080,10 @@
         <v>96</v>
       </c>
       <c r="B901" t="s" s="2">
+        <v>1900</v>
+      </c>
+      <c r="C901" t="s" s="2">
         <v>1901</v>
-      </c>
-      <c r="C901" t="s" s="2">
-        <v>1902</v>
       </c>
       <c r="D901" s="2"/>
     </row>
@@ -18071,10 +18092,10 @@
         <v>96</v>
       </c>
       <c r="B902" t="s" s="2">
+        <v>1902</v>
+      </c>
+      <c r="C902" t="s" s="2">
         <v>1903</v>
-      </c>
-      <c r="C902" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="D902" s="2"/>
     </row>
@@ -18098,7 +18119,7 @@
         <v>1906</v>
       </c>
       <c r="C904" t="s" s="2">
-        <v>1907</v>
+        <v>322</v>
       </c>
       <c r="D904" s="2"/>
     </row>
@@ -18107,10 +18128,10 @@
         <v>96</v>
       </c>
       <c r="B905" t="s" s="2">
+        <v>1907</v>
+      </c>
+      <c r="C905" t="s" s="2">
         <v>1908</v>
-      </c>
-      <c r="C905" t="s" s="2">
-        <v>1909</v>
       </c>
       <c r="D905" s="2"/>
     </row>
@@ -18119,10 +18140,10 @@
         <v>96</v>
       </c>
       <c r="B906" t="s" s="2">
+        <v>1909</v>
+      </c>
+      <c r="C906" t="s" s="2">
         <v>1910</v>
-      </c>
-      <c r="C906" t="s" s="2">
-        <v>1911</v>
       </c>
       <c r="D906" s="2"/>
     </row>
@@ -18131,10 +18152,10 @@
         <v>96</v>
       </c>
       <c r="B907" t="s" s="2">
+        <v>1911</v>
+      </c>
+      <c r="C907" t="s" s="2">
         <v>1912</v>
-      </c>
-      <c r="C907" t="s" s="2">
-        <v>1913</v>
       </c>
       <c r="D907" s="2"/>
     </row>
@@ -18143,10 +18164,10 @@
         <v>96</v>
       </c>
       <c r="B908" t="s" s="2">
+        <v>1913</v>
+      </c>
+      <c r="C908" t="s" s="2">
         <v>1914</v>
-      </c>
-      <c r="C908" t="s" s="2">
-        <v>1915</v>
       </c>
       <c r="D908" s="2"/>
     </row>
@@ -18155,10 +18176,10 @@
         <v>96</v>
       </c>
       <c r="B909" t="s" s="2">
+        <v>1915</v>
+      </c>
+      <c r="C909" t="s" s="2">
         <v>1916</v>
-      </c>
-      <c r="C909" t="s" s="2">
-        <v>1917</v>
       </c>
       <c r="D909" s="2"/>
     </row>
@@ -18167,10 +18188,10 @@
         <v>96</v>
       </c>
       <c r="B910" t="s" s="2">
+        <v>1917</v>
+      </c>
+      <c r="C910" t="s" s="2">
         <v>1918</v>
-      </c>
-      <c r="C910" t="s" s="2">
-        <v>1919</v>
       </c>
       <c r="D910" s="2"/>
     </row>
@@ -18179,10 +18200,10 @@
         <v>96</v>
       </c>
       <c r="B911" t="s" s="2">
+        <v>1919</v>
+      </c>
+      <c r="C911" t="s" s="2">
         <v>1920</v>
-      </c>
-      <c r="C911" t="s" s="2">
-        <v>1921</v>
       </c>
       <c r="D911" s="2"/>
     </row>
@@ -18191,10 +18212,10 @@
         <v>96</v>
       </c>
       <c r="B912" t="s" s="2">
+        <v>1921</v>
+      </c>
+      <c r="C912" t="s" s="2">
         <v>1922</v>
-      </c>
-      <c r="C912" t="s" s="2">
-        <v>1923</v>
       </c>
       <c r="D912" s="2"/>
     </row>
@@ -18203,10 +18224,10 @@
         <v>96</v>
       </c>
       <c r="B913" t="s" s="2">
+        <v>1923</v>
+      </c>
+      <c r="C913" t="s" s="2">
         <v>1924</v>
-      </c>
-      <c r="C913" t="s" s="2">
-        <v>1925</v>
       </c>
       <c r="D913" s="2"/>
     </row>
@@ -18215,10 +18236,10 @@
         <v>96</v>
       </c>
       <c r="B914" t="s" s="2">
+        <v>1925</v>
+      </c>
+      <c r="C914" t="s" s="2">
         <v>1926</v>
-      </c>
-      <c r="C914" t="s" s="2">
-        <v>1927</v>
       </c>
       <c r="D914" s="2"/>
     </row>
@@ -18227,10 +18248,10 @@
         <v>96</v>
       </c>
       <c r="B915" t="s" s="2">
+        <v>1927</v>
+      </c>
+      <c r="C915" t="s" s="2">
         <v>1928</v>
-      </c>
-      <c r="C915" t="s" s="2">
-        <v>1929</v>
       </c>
       <c r="D915" s="2"/>
     </row>
@@ -18239,10 +18260,10 @@
         <v>96</v>
       </c>
       <c r="B916" t="s" s="2">
+        <v>1929</v>
+      </c>
+      <c r="C916" t="s" s="2">
         <v>1930</v>
-      </c>
-      <c r="C916" t="s" s="2">
-        <v>1931</v>
       </c>
       <c r="D916" s="2"/>
     </row>
@@ -18251,10 +18272,10 @@
         <v>96</v>
       </c>
       <c r="B917" t="s" s="2">
+        <v>1931</v>
+      </c>
+      <c r="C917" t="s" s="2">
         <v>1932</v>
-      </c>
-      <c r="C917" t="s" s="2">
-        <v>1933</v>
       </c>
       <c r="D917" s="2"/>
     </row>
@@ -18263,10 +18284,10 @@
         <v>96</v>
       </c>
       <c r="B918" t="s" s="2">
+        <v>1933</v>
+      </c>
+      <c r="C918" t="s" s="2">
         <v>1934</v>
-      </c>
-      <c r="C918" t="s" s="2">
-        <v>1935</v>
       </c>
       <c r="D918" s="2"/>
     </row>
@@ -18275,10 +18296,10 @@
         <v>96</v>
       </c>
       <c r="B919" t="s" s="2">
+        <v>1935</v>
+      </c>
+      <c r="C919" t="s" s="2">
         <v>1936</v>
-      </c>
-      <c r="C919" t="s" s="2">
-        <v>1937</v>
       </c>
       <c r="D919" s="2"/>
     </row>
@@ -18287,10 +18308,10 @@
         <v>96</v>
       </c>
       <c r="B920" t="s" s="2">
+        <v>1937</v>
+      </c>
+      <c r="C920" t="s" s="2">
         <v>1938</v>
-      </c>
-      <c r="C920" t="s" s="2">
-        <v>1939</v>
       </c>
       <c r="D920" s="2"/>
     </row>
@@ -18299,10 +18320,10 @@
         <v>96</v>
       </c>
       <c r="B921" t="s" s="2">
+        <v>1939</v>
+      </c>
+      <c r="C921" t="s" s="2">
         <v>1940</v>
-      </c>
-      <c r="C921" t="s" s="2">
-        <v>1941</v>
       </c>
       <c r="D921" s="2"/>
     </row>
@@ -18311,10 +18332,10 @@
         <v>96</v>
       </c>
       <c r="B922" t="s" s="2">
+        <v>1941</v>
+      </c>
+      <c r="C922" t="s" s="2">
         <v>1942</v>
-      </c>
-      <c r="C922" t="s" s="2">
-        <v>1943</v>
       </c>
       <c r="D922" s="2"/>
     </row>
@@ -18323,10 +18344,10 @@
         <v>96</v>
       </c>
       <c r="B923" t="s" s="2">
+        <v>1943</v>
+      </c>
+      <c r="C923" t="s" s="2">
         <v>1944</v>
-      </c>
-      <c r="C923" t="s" s="2">
-        <v>1945</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -18335,10 +18356,10 @@
         <v>96</v>
       </c>
       <c r="B924" t="s" s="2">
+        <v>1945</v>
+      </c>
+      <c r="C924" t="s" s="2">
         <v>1946</v>
-      </c>
-      <c r="C924" t="s" s="2">
-        <v>1947</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -18347,10 +18368,10 @@
         <v>96</v>
       </c>
       <c r="B925" t="s" s="2">
+        <v>1947</v>
+      </c>
+      <c r="C925" t="s" s="2">
         <v>1948</v>
-      </c>
-      <c r="C925" t="s" s="2">
-        <v>1949</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -18359,10 +18380,10 @@
         <v>96</v>
       </c>
       <c r="B926" t="s" s="2">
+        <v>1949</v>
+      </c>
+      <c r="C926" t="s" s="2">
         <v>1950</v>
-      </c>
-      <c r="C926" t="s" s="2">
-        <v>1951</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -18371,10 +18392,10 @@
         <v>96</v>
       </c>
       <c r="B927" t="s" s="2">
+        <v>1951</v>
+      </c>
+      <c r="C927" t="s" s="2">
         <v>1952</v>
-      </c>
-      <c r="C927" t="s" s="2">
-        <v>1953</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -18383,10 +18404,10 @@
         <v>96</v>
       </c>
       <c r="B928" t="s" s="2">
+        <v>1953</v>
+      </c>
+      <c r="C928" t="s" s="2">
         <v>1954</v>
-      </c>
-      <c r="C928" t="s" s="2">
-        <v>1955</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -18395,10 +18416,10 @@
         <v>96</v>
       </c>
       <c r="B929" t="s" s="2">
+        <v>1955</v>
+      </c>
+      <c r="C929" t="s" s="2">
         <v>1956</v>
-      </c>
-      <c r="C929" t="s" s="2">
-        <v>1957</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -18407,10 +18428,10 @@
         <v>96</v>
       </c>
       <c r="B930" t="s" s="2">
+        <v>1957</v>
+      </c>
+      <c r="C930" t="s" s="2">
         <v>1958</v>
-      </c>
-      <c r="C930" t="s" s="2">
-        <v>1959</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -18419,10 +18440,10 @@
         <v>96</v>
       </c>
       <c r="B931" t="s" s="2">
+        <v>1959</v>
+      </c>
+      <c r="C931" t="s" s="2">
         <v>1960</v>
-      </c>
-      <c r="C931" t="s" s="2">
-        <v>1961</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -18431,10 +18452,10 @@
         <v>96</v>
       </c>
       <c r="B932" t="s" s="2">
+        <v>1961</v>
+      </c>
+      <c r="C932" t="s" s="2">
         <v>1962</v>
-      </c>
-      <c r="C932" t="s" s="2">
-        <v>1963</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -18443,10 +18464,10 @@
         <v>96</v>
       </c>
       <c r="B933" t="s" s="2">
+        <v>1963</v>
+      </c>
+      <c r="C933" t="s" s="2">
         <v>1964</v>
-      </c>
-      <c r="C933" t="s" s="2">
-        <v>1965</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -18455,10 +18476,10 @@
         <v>96</v>
       </c>
       <c r="B934" t="s" s="2">
+        <v>1965</v>
+      </c>
+      <c r="C934" t="s" s="2">
         <v>1966</v>
-      </c>
-      <c r="C934" t="s" s="2">
-        <v>1967</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -18467,10 +18488,10 @@
         <v>96</v>
       </c>
       <c r="B935" t="s" s="2">
+        <v>1967</v>
+      </c>
+      <c r="C935" t="s" s="2">
         <v>1968</v>
-      </c>
-      <c r="C935" t="s" s="2">
-        <v>1969</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -18479,10 +18500,10 @@
         <v>96</v>
       </c>
       <c r="B936" t="s" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C936" t="s" s="2">
         <v>1970</v>
-      </c>
-      <c r="C936" t="s" s="2">
-        <v>1971</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -18491,10 +18512,10 @@
         <v>96</v>
       </c>
       <c r="B937" t="s" s="2">
+        <v>1971</v>
+      </c>
+      <c r="C937" t="s" s="2">
         <v>1972</v>
-      </c>
-      <c r="C937" t="s" s="2">
-        <v>1973</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -18503,10 +18524,10 @@
         <v>96</v>
       </c>
       <c r="B938" t="s" s="2">
+        <v>1973</v>
+      </c>
+      <c r="C938" t="s" s="2">
         <v>1974</v>
-      </c>
-      <c r="C938" t="s" s="2">
-        <v>1975</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -18515,10 +18536,10 @@
         <v>96</v>
       </c>
       <c r="B939" t="s" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C939" t="s" s="2">
         <v>1976</v>
-      </c>
-      <c r="C939" t="s" s="2">
-        <v>1977</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -18527,10 +18548,10 @@
         <v>96</v>
       </c>
       <c r="B940" t="s" s="2">
+        <v>1977</v>
+      </c>
+      <c r="C940" t="s" s="2">
         <v>1978</v>
-      </c>
-      <c r="C940" t="s" s="2">
-        <v>1979</v>
       </c>
       <c r="D940" s="2"/>
     </row>
@@ -18539,10 +18560,10 @@
         <v>96</v>
       </c>
       <c r="B941" t="s" s="2">
+        <v>1979</v>
+      </c>
+      <c r="C941" t="s" s="2">
         <v>1980</v>
-      </c>
-      <c r="C941" t="s" s="2">
-        <v>1981</v>
       </c>
       <c r="D941" s="2"/>
     </row>
@@ -18551,10 +18572,10 @@
         <v>96</v>
       </c>
       <c r="B942" t="s" s="2">
+        <v>1981</v>
+      </c>
+      <c r="C942" t="s" s="2">
         <v>1982</v>
-      </c>
-      <c r="C942" t="s" s="2">
-        <v>1983</v>
       </c>
       <c r="D942" s="2"/>
     </row>
@@ -18563,10 +18584,10 @@
         <v>96</v>
       </c>
       <c r="B943" t="s" s="2">
+        <v>1983</v>
+      </c>
+      <c r="C943" t="s" s="2">
         <v>1984</v>
-      </c>
-      <c r="C943" t="s" s="2">
-        <v>1985</v>
       </c>
       <c r="D943" s="2"/>
     </row>
@@ -18575,10 +18596,10 @@
         <v>96</v>
       </c>
       <c r="B944" t="s" s="2">
+        <v>1985</v>
+      </c>
+      <c r="C944" t="s" s="2">
         <v>1986</v>
-      </c>
-      <c r="C944" t="s" s="2">
-        <v>1987</v>
       </c>
       <c r="D944" s="2"/>
     </row>
@@ -18587,10 +18608,10 @@
         <v>96</v>
       </c>
       <c r="B945" t="s" s="2">
+        <v>1987</v>
+      </c>
+      <c r="C945" t="s" s="2">
         <v>1988</v>
-      </c>
-      <c r="C945" t="s" s="2">
-        <v>1989</v>
       </c>
       <c r="D945" s="2"/>
     </row>
@@ -18599,10 +18620,10 @@
         <v>96</v>
       </c>
       <c r="B946" t="s" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C946" t="s" s="2">
         <v>1990</v>
-      </c>
-      <c r="C946" t="s" s="2">
-        <v>1991</v>
       </c>
       <c r="D946" s="2"/>
     </row>
@@ -18611,10 +18632,10 @@
         <v>96</v>
       </c>
       <c r="B947" t="s" s="2">
+        <v>1991</v>
+      </c>
+      <c r="C947" t="s" s="2">
         <v>1992</v>
-      </c>
-      <c r="C947" t="s" s="2">
-        <v>1993</v>
       </c>
       <c r="D947" s="2"/>
     </row>
@@ -18623,10 +18644,10 @@
         <v>96</v>
       </c>
       <c r="B948" t="s" s="2">
+        <v>1993</v>
+      </c>
+      <c r="C948" t="s" s="2">
         <v>1994</v>
-      </c>
-      <c r="C948" t="s" s="2">
-        <v>1995</v>
       </c>
       <c r="D948" s="2"/>
     </row>
@@ -18635,10 +18656,10 @@
         <v>96</v>
       </c>
       <c r="B949" t="s" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C949" t="s" s="2">
         <v>1996</v>
-      </c>
-      <c r="C949" t="s" s="2">
-        <v>1997</v>
       </c>
       <c r="D949" s="2"/>
     </row>
@@ -18647,10 +18668,10 @@
         <v>96</v>
       </c>
       <c r="B950" t="s" s="2">
+        <v>1997</v>
+      </c>
+      <c r="C950" t="s" s="2">
         <v>1998</v>
-      </c>
-      <c r="C950" t="s" s="2">
-        <v>1999</v>
       </c>
       <c r="D950" s="2"/>
     </row>
@@ -18659,10 +18680,10 @@
         <v>96</v>
       </c>
       <c r="B951" t="s" s="2">
+        <v>1999</v>
+      </c>
+      <c r="C951" t="s" s="2">
         <v>2000</v>
-      </c>
-      <c r="C951" t="s" s="2">
-        <v>2001</v>
       </c>
       <c r="D951" s="2"/>
     </row>
@@ -18671,10 +18692,10 @@
         <v>96</v>
       </c>
       <c r="B952" t="s" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C952" t="s" s="2">
         <v>2002</v>
-      </c>
-      <c r="C952" t="s" s="2">
-        <v>2003</v>
       </c>
       <c r="D952" s="2"/>
     </row>
@@ -18683,10 +18704,10 @@
         <v>96</v>
       </c>
       <c r="B953" t="s" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C953" t="s" s="2">
         <v>2004</v>
-      </c>
-      <c r="C953" t="s" s="2">
-        <v>2005</v>
       </c>
       <c r="D953" s="2"/>
     </row>
@@ -18695,10 +18716,10 @@
         <v>96</v>
       </c>
       <c r="B954" t="s" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C954" t="s" s="2">
         <v>2006</v>
-      </c>
-      <c r="C954" t="s" s="2">
-        <v>2007</v>
       </c>
       <c r="D954" s="2"/>
     </row>
@@ -18707,10 +18728,10 @@
         <v>96</v>
       </c>
       <c r="B955" t="s" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C955" t="s" s="2">
         <v>2008</v>
-      </c>
-      <c r="C955" t="s" s="2">
-        <v>2009</v>
       </c>
       <c r="D955" s="2"/>
     </row>
@@ -18719,10 +18740,10 @@
         <v>96</v>
       </c>
       <c r="B956" t="s" s="2">
+        <v>2009</v>
+      </c>
+      <c r="C956" t="s" s="2">
         <v>2010</v>
-      </c>
-      <c r="C956" t="s" s="2">
-        <v>2011</v>
       </c>
       <c r="D956" s="2"/>
     </row>
@@ -18731,10 +18752,10 @@
         <v>96</v>
       </c>
       <c r="B957" t="s" s="2">
+        <v>2011</v>
+      </c>
+      <c r="C957" t="s" s="2">
         <v>2012</v>
-      </c>
-      <c r="C957" t="s" s="2">
-        <v>2013</v>
       </c>
       <c r="D957" s="2"/>
     </row>
@@ -18743,10 +18764,10 @@
         <v>96</v>
       </c>
       <c r="B958" t="s" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C958" t="s" s="2">
         <v>2014</v>
-      </c>
-      <c r="C958" t="s" s="2">
-        <v>2015</v>
       </c>
       <c r="D958" s="2"/>
     </row>
@@ -18755,10 +18776,10 @@
         <v>96</v>
       </c>
       <c r="B959" t="s" s="2">
+        <v>2015</v>
+      </c>
+      <c r="C959" t="s" s="2">
         <v>2016</v>
-      </c>
-      <c r="C959" t="s" s="2">
-        <v>2017</v>
       </c>
       <c r="D959" s="2"/>
     </row>
@@ -18767,10 +18788,10 @@
         <v>96</v>
       </c>
       <c r="B960" t="s" s="2">
+        <v>2017</v>
+      </c>
+      <c r="C960" t="s" s="2">
         <v>2018</v>
-      </c>
-      <c r="C960" t="s" s="2">
-        <v>2019</v>
       </c>
       <c r="D960" s="2"/>
     </row>
@@ -18779,10 +18800,10 @@
         <v>96</v>
       </c>
       <c r="B961" t="s" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C961" t="s" s="2">
         <v>2020</v>
-      </c>
-      <c r="C961" t="s" s="2">
-        <v>2021</v>
       </c>
       <c r="D961" s="2"/>
     </row>
@@ -18791,10 +18812,10 @@
         <v>96</v>
       </c>
       <c r="B962" t="s" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C962" t="s" s="2">
         <v>2022</v>
-      </c>
-      <c r="C962" t="s" s="2">
-        <v>2023</v>
       </c>
       <c r="D962" s="2"/>
     </row>
@@ -18803,10 +18824,10 @@
         <v>96</v>
       </c>
       <c r="B963" t="s" s="2">
+        <v>2023</v>
+      </c>
+      <c r="C963" t="s" s="2">
         <v>2024</v>
-      </c>
-      <c r="C963" t="s" s="2">
-        <v>2025</v>
       </c>
       <c r="D963" s="2"/>
     </row>
@@ -18815,10 +18836,10 @@
         <v>96</v>
       </c>
       <c r="B964" t="s" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C964" t="s" s="2">
         <v>2026</v>
-      </c>
-      <c r="C964" t="s" s="2">
-        <v>2027</v>
       </c>
       <c r="D964" s="2"/>
     </row>
@@ -18827,10 +18848,10 @@
         <v>96</v>
       </c>
       <c r="B965" t="s" s="2">
+        <v>2027</v>
+      </c>
+      <c r="C965" t="s" s="2">
         <v>2028</v>
-      </c>
-      <c r="C965" t="s" s="2">
-        <v>2029</v>
       </c>
       <c r="D965" s="2"/>
     </row>
@@ -18839,10 +18860,10 @@
         <v>96</v>
       </c>
       <c r="B966" t="s" s="2">
+        <v>2029</v>
+      </c>
+      <c r="C966" t="s" s="2">
         <v>2030</v>
-      </c>
-      <c r="C966" t="s" s="2">
-        <v>2031</v>
       </c>
       <c r="D966" s="2"/>
     </row>
@@ -18851,10 +18872,10 @@
         <v>96</v>
       </c>
       <c r="B967" t="s" s="2">
+        <v>2031</v>
+      </c>
+      <c r="C967" t="s" s="2">
         <v>2032</v>
-      </c>
-      <c r="C967" t="s" s="2">
-        <v>2033</v>
       </c>
       <c r="D967" s="2"/>
     </row>
@@ -18863,10 +18884,10 @@
         <v>96</v>
       </c>
       <c r="B968" t="s" s="2">
+        <v>2033</v>
+      </c>
+      <c r="C968" t="s" s="2">
         <v>2034</v>
-      </c>
-      <c r="C968" t="s" s="2">
-        <v>2035</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -18875,10 +18896,10 @@
         <v>96</v>
       </c>
       <c r="B969" t="s" s="2">
+        <v>2035</v>
+      </c>
+      <c r="C969" t="s" s="2">
         <v>2036</v>
-      </c>
-      <c r="C969" t="s" s="2">
-        <v>2037</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -18887,10 +18908,10 @@
         <v>96</v>
       </c>
       <c r="B970" t="s" s="2">
+        <v>2037</v>
+      </c>
+      <c r="C970" t="s" s="2">
         <v>2038</v>
-      </c>
-      <c r="C970" t="s" s="2">
-        <v>2039</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -18899,10 +18920,10 @@
         <v>96</v>
       </c>
       <c r="B971" t="s" s="2">
+        <v>2039</v>
+      </c>
+      <c r="C971" t="s" s="2">
         <v>2040</v>
-      </c>
-      <c r="C971" t="s" s="2">
-        <v>2041</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -18911,10 +18932,10 @@
         <v>96</v>
       </c>
       <c r="B972" t="s" s="2">
+        <v>2041</v>
+      </c>
+      <c r="C972" t="s" s="2">
         <v>2042</v>
-      </c>
-      <c r="C972" t="s" s="2">
-        <v>2043</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -18923,10 +18944,10 @@
         <v>96</v>
       </c>
       <c r="B973" t="s" s="2">
+        <v>2043</v>
+      </c>
+      <c r="C973" t="s" s="2">
         <v>2044</v>
-      </c>
-      <c r="C973" t="s" s="2">
-        <v>2045</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -18935,10 +18956,10 @@
         <v>96</v>
       </c>
       <c r="B974" t="s" s="2">
+        <v>2045</v>
+      </c>
+      <c r="C974" t="s" s="2">
         <v>2046</v>
-      </c>
-      <c r="C974" t="s" s="2">
-        <v>2047</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -18947,10 +18968,10 @@
         <v>96</v>
       </c>
       <c r="B975" t="s" s="2">
+        <v>2047</v>
+      </c>
+      <c r="C975" t="s" s="2">
         <v>2048</v>
-      </c>
-      <c r="C975" t="s" s="2">
-        <v>2049</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -18959,10 +18980,10 @@
         <v>96</v>
       </c>
       <c r="B976" t="s" s="2">
+        <v>2049</v>
+      </c>
+      <c r="C976" t="s" s="2">
         <v>2050</v>
-      </c>
-      <c r="C976" t="s" s="2">
-        <v>2051</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -18971,10 +18992,10 @@
         <v>96</v>
       </c>
       <c r="B977" t="s" s="2">
+        <v>2051</v>
+      </c>
+      <c r="C977" t="s" s="2">
         <v>2052</v>
-      </c>
-      <c r="C977" t="s" s="2">
-        <v>2053</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -18983,10 +19004,10 @@
         <v>96</v>
       </c>
       <c r="B978" t="s" s="2">
+        <v>2053</v>
+      </c>
+      <c r="C978" t="s" s="2">
         <v>2054</v>
-      </c>
-      <c r="C978" t="s" s="2">
-        <v>2055</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -18995,10 +19016,10 @@
         <v>96</v>
       </c>
       <c r="B979" t="s" s="2">
+        <v>2055</v>
+      </c>
+      <c r="C979" t="s" s="2">
         <v>2056</v>
-      </c>
-      <c r="C979" t="s" s="2">
-        <v>2057</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -19007,10 +19028,10 @@
         <v>96</v>
       </c>
       <c r="B980" t="s" s="2">
+        <v>2057</v>
+      </c>
+      <c r="C980" t="s" s="2">
         <v>2058</v>
-      </c>
-      <c r="C980" t="s" s="2">
-        <v>2059</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -19019,10 +19040,10 @@
         <v>96</v>
       </c>
       <c r="B981" t="s" s="2">
+        <v>2059</v>
+      </c>
+      <c r="C981" t="s" s="2">
         <v>2060</v>
-      </c>
-      <c r="C981" t="s" s="2">
-        <v>2061</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -19031,10 +19052,10 @@
         <v>96</v>
       </c>
       <c r="B982" t="s" s="2">
+        <v>2061</v>
+      </c>
+      <c r="C982" t="s" s="2">
         <v>2062</v>
-      </c>
-      <c r="C982" t="s" s="2">
-        <v>2063</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -19043,10 +19064,10 @@
         <v>96</v>
       </c>
       <c r="B983" t="s" s="2">
+        <v>2063</v>
+      </c>
+      <c r="C983" t="s" s="2">
         <v>2064</v>
-      </c>
-      <c r="C983" t="s" s="2">
-        <v>2065</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -19055,10 +19076,10 @@
         <v>96</v>
       </c>
       <c r="B984" t="s" s="2">
+        <v>2065</v>
+      </c>
+      <c r="C984" t="s" s="2">
         <v>2066</v>
-      </c>
-      <c r="C984" t="s" s="2">
-        <v>2067</v>
       </c>
       <c r="D984" s="2"/>
     </row>
@@ -19067,10 +19088,10 @@
         <v>96</v>
       </c>
       <c r="B985" t="s" s="2">
+        <v>2067</v>
+      </c>
+      <c r="C985" t="s" s="2">
         <v>2068</v>
-      </c>
-      <c r="C985" t="s" s="2">
-        <v>2069</v>
       </c>
       <c r="D985" s="2"/>
     </row>
@@ -19079,10 +19100,10 @@
         <v>96</v>
       </c>
       <c r="B986" t="s" s="2">
+        <v>2069</v>
+      </c>
+      <c r="C986" t="s" s="2">
         <v>2070</v>
-      </c>
-      <c r="C986" t="s" s="2">
-        <v>2071</v>
       </c>
       <c r="D986" s="2"/>
     </row>
@@ -19091,10 +19112,10 @@
         <v>96</v>
       </c>
       <c r="B987" t="s" s="2">
+        <v>2071</v>
+      </c>
+      <c r="C987" t="s" s="2">
         <v>2072</v>
-      </c>
-      <c r="C987" t="s" s="2">
-        <v>2073</v>
       </c>
       <c r="D987" s="2"/>
     </row>
@@ -19103,10 +19124,10 @@
         <v>96</v>
       </c>
       <c r="B988" t="s" s="2">
+        <v>2073</v>
+      </c>
+      <c r="C988" t="s" s="2">
         <v>2074</v>
-      </c>
-      <c r="C988" t="s" s="2">
-        <v>2075</v>
       </c>
       <c r="D988" s="2"/>
     </row>
@@ -19115,10 +19136,10 @@
         <v>96</v>
       </c>
       <c r="B989" t="s" s="2">
+        <v>2075</v>
+      </c>
+      <c r="C989" t="s" s="2">
         <v>2076</v>
-      </c>
-      <c r="C989" t="s" s="2">
-        <v>2077</v>
       </c>
       <c r="D989" s="2"/>
     </row>
@@ -19127,10 +19148,10 @@
         <v>96</v>
       </c>
       <c r="B990" t="s" s="2">
+        <v>2077</v>
+      </c>
+      <c r="C990" t="s" s="2">
         <v>2078</v>
-      </c>
-      <c r="C990" t="s" s="2">
-        <v>2079</v>
       </c>
       <c r="D990" s="2"/>
     </row>
@@ -19139,10 +19160,10 @@
         <v>96</v>
       </c>
       <c r="B991" t="s" s="2">
+        <v>2079</v>
+      </c>
+      <c r="C991" t="s" s="2">
         <v>2080</v>
-      </c>
-      <c r="C991" t="s" s="2">
-        <v>2081</v>
       </c>
       <c r="D991" s="2"/>
     </row>
@@ -19151,10 +19172,10 @@
         <v>96</v>
       </c>
       <c r="B992" t="s" s="2">
+        <v>2081</v>
+      </c>
+      <c r="C992" t="s" s="2">
         <v>2082</v>
-      </c>
-      <c r="C992" t="s" s="2">
-        <v>2083</v>
       </c>
       <c r="D992" s="2"/>
     </row>
@@ -19163,10 +19184,10 @@
         <v>96</v>
       </c>
       <c r="B993" t="s" s="2">
+        <v>2083</v>
+      </c>
+      <c r="C993" t="s" s="2">
         <v>2084</v>
-      </c>
-      <c r="C993" t="s" s="2">
-        <v>2085</v>
       </c>
       <c r="D993" s="2"/>
     </row>
@@ -19175,10 +19196,10 @@
         <v>96</v>
       </c>
       <c r="B994" t="s" s="2">
+        <v>2085</v>
+      </c>
+      <c r="C994" t="s" s="2">
         <v>2086</v>
-      </c>
-      <c r="C994" t="s" s="2">
-        <v>2087</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -19187,10 +19208,10 @@
         <v>96</v>
       </c>
       <c r="B995" t="s" s="2">
+        <v>2087</v>
+      </c>
+      <c r="C995" t="s" s="2">
         <v>2088</v>
-      </c>
-      <c r="C995" t="s" s="2">
-        <v>2089</v>
       </c>
       <c r="D995" s="2"/>
     </row>
@@ -19199,10 +19220,10 @@
         <v>96</v>
       </c>
       <c r="B996" t="s" s="2">
+        <v>2089</v>
+      </c>
+      <c r="C996" t="s" s="2">
         <v>2090</v>
-      </c>
-      <c r="C996" t="s" s="2">
-        <v>2091</v>
       </c>
       <c r="D996" s="2"/>
     </row>
@@ -19211,10 +19232,10 @@
         <v>96</v>
       </c>
       <c r="B997" t="s" s="2">
+        <v>2091</v>
+      </c>
+      <c r="C997" t="s" s="2">
         <v>2092</v>
-      </c>
-      <c r="C997" t="s" s="2">
-        <v>2093</v>
       </c>
       <c r="D997" s="2"/>
     </row>
@@ -19223,10 +19244,10 @@
         <v>96</v>
       </c>
       <c r="B998" t="s" s="2">
+        <v>2093</v>
+      </c>
+      <c r="C998" t="s" s="2">
         <v>2094</v>
-      </c>
-      <c r="C998" t="s" s="2">
-        <v>2095</v>
       </c>
       <c r="D998" s="2"/>
     </row>
@@ -19235,10 +19256,10 @@
         <v>96</v>
       </c>
       <c r="B999" t="s" s="2">
+        <v>2095</v>
+      </c>
+      <c r="C999" t="s" s="2">
         <v>2096</v>
-      </c>
-      <c r="C999" t="s" s="2">
-        <v>2097</v>
       </c>
       <c r="D999" s="2"/>
     </row>
@@ -19247,10 +19268,10 @@
         <v>96</v>
       </c>
       <c r="B1000" t="s" s="2">
+        <v>2097</v>
+      </c>
+      <c r="C1000" t="s" s="2">
         <v>2098</v>
-      </c>
-      <c r="C1000" t="s" s="2">
-        <v>2099</v>
       </c>
       <c r="D1000" s="2"/>
     </row>
@@ -19259,10 +19280,10 @@
         <v>96</v>
       </c>
       <c r="B1001" t="s" s="2">
+        <v>2099</v>
+      </c>
+      <c r="C1001" t="s" s="2">
         <v>2100</v>
-      </c>
-      <c r="C1001" t="s" s="2">
-        <v>2101</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -19271,10 +19292,10 @@
         <v>96</v>
       </c>
       <c r="B1002" t="s" s="2">
+        <v>2101</v>
+      </c>
+      <c r="C1002" t="s" s="2">
         <v>2102</v>
-      </c>
-      <c r="C1002" t="s" s="2">
-        <v>2103</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -19283,10 +19304,10 @@
         <v>96</v>
       </c>
       <c r="B1003" t="s" s="2">
+        <v>2103</v>
+      </c>
+      <c r="C1003" t="s" s="2">
         <v>2104</v>
-      </c>
-      <c r="C1003" t="s" s="2">
-        <v>2105</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -19295,10 +19316,10 @@
         <v>96</v>
       </c>
       <c r="B1004" t="s" s="2">
+        <v>2105</v>
+      </c>
+      <c r="C1004" t="s" s="2">
         <v>2106</v>
-      </c>
-      <c r="C1004" t="s" s="2">
-        <v>2107</v>
       </c>
       <c r="D1004" s="2"/>
     </row>
@@ -19307,10 +19328,10 @@
         <v>96</v>
       </c>
       <c r="B1005" t="s" s="2">
+        <v>2107</v>
+      </c>
+      <c r="C1005" t="s" s="2">
         <v>2108</v>
-      </c>
-      <c r="C1005" t="s" s="2">
-        <v>2109</v>
       </c>
       <c r="D1005" s="2"/>
     </row>
@@ -19319,10 +19340,10 @@
         <v>96</v>
       </c>
       <c r="B1006" t="s" s="2">
+        <v>2109</v>
+      </c>
+      <c r="C1006" t="s" s="2">
         <v>2110</v>
-      </c>
-      <c r="C1006" t="s" s="2">
-        <v>2111</v>
       </c>
       <c r="D1006" s="2"/>
     </row>
@@ -19331,10 +19352,10 @@
         <v>96</v>
       </c>
       <c r="B1007" t="s" s="2">
+        <v>2111</v>
+      </c>
+      <c r="C1007" t="s" s="2">
         <v>2112</v>
-      </c>
-      <c r="C1007" t="s" s="2">
-        <v>2113</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -19343,10 +19364,10 @@
         <v>96</v>
       </c>
       <c r="B1008" t="s" s="2">
+        <v>2113</v>
+      </c>
+      <c r="C1008" t="s" s="2">
         <v>2114</v>
-      </c>
-      <c r="C1008" t="s" s="2">
-        <v>2115</v>
       </c>
       <c r="D1008" s="2"/>
     </row>
@@ -19355,10 +19376,10 @@
         <v>96</v>
       </c>
       <c r="B1009" t="s" s="2">
+        <v>2115</v>
+      </c>
+      <c r="C1009" t="s" s="2">
         <v>2116</v>
-      </c>
-      <c r="C1009" t="s" s="2">
-        <v>2117</v>
       </c>
       <c r="D1009" s="2"/>
     </row>
@@ -19367,10 +19388,10 @@
         <v>96</v>
       </c>
       <c r="B1010" t="s" s="2">
+        <v>2117</v>
+      </c>
+      <c r="C1010" t="s" s="2">
         <v>2118</v>
-      </c>
-      <c r="C1010" t="s" s="2">
-        <v>2119</v>
       </c>
       <c r="D1010" s="2"/>
     </row>
@@ -19379,10 +19400,10 @@
         <v>96</v>
       </c>
       <c r="B1011" t="s" s="2">
+        <v>2119</v>
+      </c>
+      <c r="C1011" t="s" s="2">
         <v>2120</v>
-      </c>
-      <c r="C1011" t="s" s="2">
-        <v>2121</v>
       </c>
       <c r="D1011" s="2"/>
     </row>
@@ -19391,10 +19412,10 @@
         <v>96</v>
       </c>
       <c r="B1012" t="s" s="2">
+        <v>2121</v>
+      </c>
+      <c r="C1012" t="s" s="2">
         <v>2122</v>
-      </c>
-      <c r="C1012" t="s" s="2">
-        <v>2123</v>
       </c>
       <c r="D1012" s="2"/>
     </row>
@@ -19403,10 +19424,10 @@
         <v>96</v>
       </c>
       <c r="B1013" t="s" s="2">
+        <v>2123</v>
+      </c>
+      <c r="C1013" t="s" s="2">
         <v>2124</v>
-      </c>
-      <c r="C1013" t="s" s="2">
-        <v>2125</v>
       </c>
       <c r="D1013" s="2"/>
     </row>
@@ -19415,10 +19436,10 @@
         <v>96</v>
       </c>
       <c r="B1014" t="s" s="2">
+        <v>2125</v>
+      </c>
+      <c r="C1014" t="s" s="2">
         <v>2126</v>
-      </c>
-      <c r="C1014" t="s" s="2">
-        <v>2127</v>
       </c>
       <c r="D1014" s="2"/>
     </row>
@@ -19427,10 +19448,10 @@
         <v>96</v>
       </c>
       <c r="B1015" t="s" s="2">
+        <v>2127</v>
+      </c>
+      <c r="C1015" t="s" s="2">
         <v>2128</v>
-      </c>
-      <c r="C1015" t="s" s="2">
-        <v>2129</v>
       </c>
       <c r="D1015" s="2"/>
     </row>
@@ -19439,10 +19460,10 @@
         <v>96</v>
       </c>
       <c r="B1016" t="s" s="2">
+        <v>2129</v>
+      </c>
+      <c r="C1016" t="s" s="2">
         <v>2130</v>
-      </c>
-      <c r="C1016" t="s" s="2">
-        <v>2131</v>
       </c>
       <c r="D1016" s="2"/>
     </row>
@@ -19451,10 +19472,10 @@
         <v>96</v>
       </c>
       <c r="B1017" t="s" s="2">
+        <v>2131</v>
+      </c>
+      <c r="C1017" t="s" s="2">
         <v>2132</v>
-      </c>
-      <c r="C1017" t="s" s="2">
-        <v>2133</v>
       </c>
       <c r="D1017" s="2"/>
     </row>
@@ -19463,10 +19484,10 @@
         <v>96</v>
       </c>
       <c r="B1018" t="s" s="2">
+        <v>2133</v>
+      </c>
+      <c r="C1018" t="s" s="2">
         <v>2134</v>
-      </c>
-      <c r="C1018" t="s" s="2">
-        <v>2135</v>
       </c>
       <c r="D1018" s="2"/>
     </row>
@@ -19475,10 +19496,10 @@
         <v>96</v>
       </c>
       <c r="B1019" t="s" s="2">
+        <v>2135</v>
+      </c>
+      <c r="C1019" t="s" s="2">
         <v>2136</v>
-      </c>
-      <c r="C1019" t="s" s="2">
-        <v>2137</v>
       </c>
       <c r="D1019" s="2"/>
     </row>
@@ -19487,10 +19508,10 @@
         <v>96</v>
       </c>
       <c r="B1020" t="s" s="2">
+        <v>2137</v>
+      </c>
+      <c r="C1020" t="s" s="2">
         <v>2138</v>
-      </c>
-      <c r="C1020" t="s" s="2">
-        <v>2139</v>
       </c>
       <c r="D1020" s="2"/>
     </row>
@@ -19499,10 +19520,10 @@
         <v>96</v>
       </c>
       <c r="B1021" t="s" s="2">
+        <v>2139</v>
+      </c>
+      <c r="C1021" t="s" s="2">
         <v>2140</v>
-      </c>
-      <c r="C1021" t="s" s="2">
-        <v>2141</v>
       </c>
       <c r="D1021" s="2"/>
     </row>
@@ -19511,10 +19532,10 @@
         <v>96</v>
       </c>
       <c r="B1022" t="s" s="2">
+        <v>2141</v>
+      </c>
+      <c r="C1022" t="s" s="2">
         <v>2142</v>
-      </c>
-      <c r="C1022" t="s" s="2">
-        <v>2143</v>
       </c>
       <c r="D1022" s="2"/>
     </row>
@@ -19523,10 +19544,10 @@
         <v>96</v>
       </c>
       <c r="B1023" t="s" s="2">
+        <v>2143</v>
+      </c>
+      <c r="C1023" t="s" s="2">
         <v>2144</v>
-      </c>
-      <c r="C1023" t="s" s="2">
-        <v>2145</v>
       </c>
       <c r="D1023" s="2"/>
     </row>
@@ -19535,10 +19556,10 @@
         <v>96</v>
       </c>
       <c r="B1024" t="s" s="2">
+        <v>2145</v>
+      </c>
+      <c r="C1024" t="s" s="2">
         <v>2146</v>
-      </c>
-      <c r="C1024" t="s" s="2">
-        <v>2147</v>
       </c>
       <c r="D1024" s="2"/>
     </row>
@@ -19547,10 +19568,10 @@
         <v>96</v>
       </c>
       <c r="B1025" t="s" s="2">
+        <v>2147</v>
+      </c>
+      <c r="C1025" t="s" s="2">
         <v>2148</v>
-      </c>
-      <c r="C1025" t="s" s="2">
-        <v>2149</v>
       </c>
       <c r="D1025" s="2"/>
     </row>
@@ -19559,10 +19580,10 @@
         <v>96</v>
       </c>
       <c r="B1026" t="s" s="2">
+        <v>2149</v>
+      </c>
+      <c r="C1026" t="s" s="2">
         <v>2150</v>
-      </c>
-      <c r="C1026" t="s" s="2">
-        <v>2151</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -19571,10 +19592,10 @@
         <v>96</v>
       </c>
       <c r="B1027" t="s" s="2">
+        <v>2151</v>
+      </c>
+      <c r="C1027" t="s" s="2">
         <v>2152</v>
-      </c>
-      <c r="C1027" t="s" s="2">
-        <v>2153</v>
       </c>
       <c r="D1027" s="2"/>
     </row>
@@ -19583,10 +19604,10 @@
         <v>96</v>
       </c>
       <c r="B1028" t="s" s="2">
+        <v>2153</v>
+      </c>
+      <c r="C1028" t="s" s="2">
         <v>2154</v>
-      </c>
-      <c r="C1028" t="s" s="2">
-        <v>2155</v>
       </c>
       <c r="D1028" s="2"/>
     </row>
@@ -19595,10 +19616,10 @@
         <v>96</v>
       </c>
       <c r="B1029" t="s" s="2">
+        <v>2155</v>
+      </c>
+      <c r="C1029" t="s" s="2">
         <v>2156</v>
-      </c>
-      <c r="C1029" t="s" s="2">
-        <v>2157</v>
       </c>
       <c r="D1029" s="2"/>
     </row>
@@ -19607,10 +19628,10 @@
         <v>96</v>
       </c>
       <c r="B1030" t="s" s="2">
+        <v>2157</v>
+      </c>
+      <c r="C1030" t="s" s="2">
         <v>2158</v>
-      </c>
-      <c r="C1030" t="s" s="2">
-        <v>2159</v>
       </c>
       <c r="D1030" s="2"/>
     </row>
@@ -19619,10 +19640,10 @@
         <v>96</v>
       </c>
       <c r="B1031" t="s" s="2">
+        <v>2159</v>
+      </c>
+      <c r="C1031" t="s" s="2">
         <v>2160</v>
-      </c>
-      <c r="C1031" t="s" s="2">
-        <v>2161</v>
       </c>
       <c r="D1031" s="2"/>
     </row>
@@ -19631,10 +19652,10 @@
         <v>96</v>
       </c>
       <c r="B1032" t="s" s="2">
+        <v>2161</v>
+      </c>
+      <c r="C1032" t="s" s="2">
         <v>2162</v>
-      </c>
-      <c r="C1032" t="s" s="2">
-        <v>2163</v>
       </c>
       <c r="D1032" s="2"/>
     </row>
@@ -19643,10 +19664,10 @@
         <v>96</v>
       </c>
       <c r="B1033" t="s" s="2">
+        <v>2163</v>
+      </c>
+      <c r="C1033" t="s" s="2">
         <v>2164</v>
-      </c>
-      <c r="C1033" t="s" s="2">
-        <v>2165</v>
       </c>
       <c r="D1033" s="2"/>
     </row>
@@ -19655,10 +19676,10 @@
         <v>96</v>
       </c>
       <c r="B1034" t="s" s="2">
+        <v>2165</v>
+      </c>
+      <c r="C1034" t="s" s="2">
         <v>2166</v>
-      </c>
-      <c r="C1034" t="s" s="2">
-        <v>2167</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -19667,10 +19688,10 @@
         <v>96</v>
       </c>
       <c r="B1035" t="s" s="2">
+        <v>2167</v>
+      </c>
+      <c r="C1035" t="s" s="2">
         <v>2168</v>
-      </c>
-      <c r="C1035" t="s" s="2">
-        <v>2169</v>
       </c>
       <c r="D1035" s="2"/>
     </row>
@@ -19679,10 +19700,10 @@
         <v>96</v>
       </c>
       <c r="B1036" t="s" s="2">
+        <v>2169</v>
+      </c>
+      <c r="C1036" t="s" s="2">
         <v>2170</v>
-      </c>
-      <c r="C1036" t="s" s="2">
-        <v>2171</v>
       </c>
       <c r="D1036" s="2"/>
     </row>
@@ -19691,10 +19712,10 @@
         <v>96</v>
       </c>
       <c r="B1037" t="s" s="2">
+        <v>2171</v>
+      </c>
+      <c r="C1037" t="s" s="2">
         <v>2172</v>
-      </c>
-      <c r="C1037" t="s" s="2">
-        <v>2173</v>
       </c>
       <c r="D1037" s="2"/>
     </row>
@@ -19703,10 +19724,10 @@
         <v>96</v>
       </c>
       <c r="B1038" t="s" s="2">
+        <v>2173</v>
+      </c>
+      <c r="C1038" t="s" s="2">
         <v>2174</v>
-      </c>
-      <c r="C1038" t="s" s="2">
-        <v>2175</v>
       </c>
       <c r="D1038" s="2"/>
     </row>
@@ -19715,10 +19736,10 @@
         <v>96</v>
       </c>
       <c r="B1039" t="s" s="2">
+        <v>2175</v>
+      </c>
+      <c r="C1039" t="s" s="2">
         <v>2176</v>
-      </c>
-      <c r="C1039" t="s" s="2">
-        <v>2177</v>
       </c>
       <c r="D1039" s="2"/>
     </row>
@@ -19727,10 +19748,10 @@
         <v>96</v>
       </c>
       <c r="B1040" t="s" s="2">
+        <v>2177</v>
+      </c>
+      <c r="C1040" t="s" s="2">
         <v>2178</v>
-      </c>
-      <c r="C1040" t="s" s="2">
-        <v>2179</v>
       </c>
       <c r="D1040" s="2"/>
     </row>
@@ -19739,10 +19760,10 @@
         <v>96</v>
       </c>
       <c r="B1041" t="s" s="2">
-        <v>10</v>
+        <v>2179</v>
       </c>
       <c r="C1041" t="s" s="2">
-        <v>10</v>
+        <v>2180</v>
       </c>
       <c r="D1041" s="2"/>
     </row>
@@ -19751,10 +19772,10 @@
         <v>96</v>
       </c>
       <c r="B1042" t="s" s="2">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C1042" t="s" s="2">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="D1042" s="2"/>
     </row>
@@ -19763,10 +19784,10 @@
         <v>96</v>
       </c>
       <c r="B1043" t="s" s="2">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C1043" t="s" s="2">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="D1043" s="2"/>
     </row>
@@ -19775,10 +19796,10 @@
         <v>96</v>
       </c>
       <c r="B1044" t="s" s="2">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="C1044" t="s" s="2">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="D1044" s="2"/>
     </row>
@@ -19787,10 +19808,10 @@
         <v>96</v>
       </c>
       <c r="B1045" t="s" s="2">
-        <v>2186</v>
+        <v>10</v>
       </c>
       <c r="C1045" t="s" s="2">
-        <v>2187</v>
+        <v>10</v>
       </c>
       <c r="D1045" s="2"/>
     </row>
@@ -19799,10 +19820,10 @@
         <v>96</v>
       </c>
       <c r="B1046" t="s" s="2">
+        <v>2187</v>
+      </c>
+      <c r="C1046" t="s" s="2">
         <v>2188</v>
-      </c>
-      <c r="C1046" t="s" s="2">
-        <v>2189</v>
       </c>
       <c r="D1046" s="2"/>
     </row>
@@ -19811,12 +19832,60 @@
         <v>96</v>
       </c>
       <c r="B1047" t="s" s="2">
+        <v>2189</v>
+      </c>
+      <c r="C1047" t="s" s="2">
         <v>2190</v>
       </c>
-      <c r="C1047" t="s" s="2">
+      <c r="D1047" s="2"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1048" t="s" s="2">
         <v>2191</v>
       </c>
-      <c r="D1047" s="2"/>
+      <c r="C1048" t="s" s="2">
+        <v>2192</v>
+      </c>
+      <c r="D1048" s="2"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1049" t="s" s="2">
+        <v>2193</v>
+      </c>
+      <c r="C1049" t="s" s="2">
+        <v>2194</v>
+      </c>
+      <c r="D1049" s="2"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1050" t="s" s="2">
+        <v>2195</v>
+      </c>
+      <c r="C1050" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="D1050" s="2"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B1051" t="s" s="2">
+        <v>2197</v>
+      </c>
+      <c r="C1051" t="s" s="2">
+        <v>2198</v>
+      </c>
+      <c r="D1051" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
